--- a/research/traditional_assets/database/data/mexico/mexico_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_hospitals_healthcare_facilities.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08461962913543611</v>
+        <v>0.08439727024802979</v>
       </c>
       <c r="C2">
-        <v>225.7941138807</v>
+        <v>224.1481186588825</v>
       </c>
       <c r="D2">
-        <v>176.0941138807</v>
+        <v>176.7311186588824</v>
       </c>
       <c r="E2">
-        <v>-52.2</v>
+        <v>-49.917</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.283</v>
       </c>
       <c r="G2">
         <v>49.7</v>
@@ -1451,28 +1451,28 @@
         <v>25.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1148349</v>
       </c>
       <c r="N2">
-        <v>25.8</v>
+        <v>25.6851651</v>
       </c>
       <c r="O2">
-        <v>7.74</v>
+        <v>7.705549529999999</v>
       </c>
       <c r="P2">
-        <v>18.06</v>
+        <v>17.97961557</v>
       </c>
       <c r="Q2">
-        <v>26.26</v>
+        <v>26.17961557</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08461962913543611</v>
+        <v>0.08489411136164626</v>
       </c>
       <c r="T2">
-        <v>0.5648729042001042</v>
+        <v>0.5688669550378826</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>224.6703745986629</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08439727024802979</v>
+        <v>0.08417491136062348</v>
       </c>
       <c r="C3">
-        <v>224.1481186588825</v>
+        <v>222.5067487849861</v>
       </c>
       <c r="D3">
-        <v>176.7311186588824</v>
+        <v>177.3727487849861</v>
       </c>
       <c r="E3">
-        <v>-49.917</v>
+        <v>-47.634</v>
       </c>
       <c r="F3">
-        <v>2.283</v>
+        <v>4.566000000000001</v>
       </c>
       <c r="G3">
         <v>49.7</v>
@@ -1533,28 +1533,28 @@
         <v>25.8</v>
       </c>
       <c r="M3">
-        <v>0.1148349</v>
+        <v>0.2296698</v>
       </c>
       <c r="N3">
-        <v>25.6851651</v>
+        <v>25.5703302</v>
       </c>
       <c r="O3">
-        <v>7.705549529999999</v>
+        <v>7.67109906</v>
       </c>
       <c r="P3">
-        <v>17.97961557</v>
+        <v>17.89923114</v>
       </c>
       <c r="Q3">
-        <v>26.17961557</v>
+        <v>26.09923114</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08489411136164626</v>
+        <v>0.08517419526594233</v>
       </c>
       <c r="T3">
-        <v>0.5688669550378826</v>
+        <v>0.5729425171172485</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>224.6703745986629</v>
+        <v>112.3351872993315</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08417491136062348</v>
+        <v>0.08395255247321716</v>
       </c>
       <c r="C4">
-        <v>222.5067487849861</v>
+        <v>220.8700548201648</v>
       </c>
       <c r="D4">
-        <v>177.3727487849861</v>
+        <v>178.0190548201648</v>
       </c>
       <c r="E4">
-        <v>-47.634</v>
+        <v>-45.351</v>
       </c>
       <c r="F4">
-        <v>4.566000000000001</v>
+        <v>6.849</v>
       </c>
       <c r="G4">
         <v>49.7</v>
@@ -1615,28 +1615,28 @@
         <v>25.8</v>
       </c>
       <c r="M4">
-        <v>0.2296698</v>
+        <v>0.3445047</v>
       </c>
       <c r="N4">
-        <v>25.5703302</v>
+        <v>25.4554953</v>
       </c>
       <c r="O4">
-        <v>7.67109906</v>
+        <v>7.636648589999999</v>
       </c>
       <c r="P4">
-        <v>17.89923114</v>
+        <v>17.81884671</v>
       </c>
       <c r="Q4">
-        <v>26.09923114</v>
+        <v>26.01884671</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08517419526594233</v>
+        <v>0.08546005409610018</v>
       </c>
       <c r="T4">
-        <v>0.5729425171172485</v>
+        <v>0.5771021114044362</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>112.3351872993315</v>
+        <v>74.89012486622099</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08395255247321716</v>
+        <v>0.08373019358581087</v>
       </c>
       <c r="C5">
-        <v>220.8700548201648</v>
+        <v>219.2380880652008</v>
       </c>
       <c r="D5">
-        <v>178.0190548201648</v>
+        <v>178.6700880652008</v>
       </c>
       <c r="E5">
-        <v>-45.351</v>
+        <v>-43.068</v>
       </c>
       <c r="F5">
-        <v>6.849</v>
+        <v>9.132000000000001</v>
       </c>
       <c r="G5">
         <v>49.7</v>
@@ -1697,28 +1697,28 @@
         <v>25.8</v>
       </c>
       <c r="M5">
-        <v>0.3445047</v>
+        <v>0.4593396000000001</v>
       </c>
       <c r="N5">
-        <v>25.4554953</v>
+        <v>25.3406604</v>
       </c>
       <c r="O5">
-        <v>7.636648589999999</v>
+        <v>7.60219812</v>
       </c>
       <c r="P5">
-        <v>17.81884671</v>
+        <v>17.73846228</v>
       </c>
       <c r="Q5">
-        <v>26.01884671</v>
+        <v>25.93846228</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08546005409610018</v>
+        <v>0.08575186831855298</v>
       </c>
       <c r="T5">
-        <v>0.5771021114044362</v>
+        <v>0.5813483639059405</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>74.89012486622099</v>
+        <v>56.16759364966573</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08373019358581087</v>
+        <v>0.08350783469840456</v>
       </c>
       <c r="C6">
-        <v>219.2380880652008</v>
+        <v>217.610900574079</v>
       </c>
       <c r="D6">
-        <v>178.6700880652008</v>
+        <v>179.325900574079</v>
       </c>
       <c r="E6">
-        <v>-43.068</v>
+        <v>-40.785</v>
       </c>
       <c r="F6">
-        <v>9.132000000000001</v>
+        <v>11.415</v>
       </c>
       <c r="G6">
         <v>49.7</v>
@@ -1779,28 +1779,28 @@
         <v>25.8</v>
       </c>
       <c r="M6">
-        <v>0.4593396000000001</v>
+        <v>0.5741745</v>
       </c>
       <c r="N6">
-        <v>25.3406604</v>
+        <v>25.2258255</v>
       </c>
       <c r="O6">
-        <v>7.60219812</v>
+        <v>7.567747649999999</v>
       </c>
       <c r="P6">
-        <v>17.73846228</v>
+        <v>17.65807785</v>
       </c>
       <c r="Q6">
-        <v>25.93846228</v>
+        <v>25.85807785</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08575186831855298</v>
+        <v>0.08604982599832059</v>
       </c>
       <c r="T6">
-        <v>0.5813483639059405</v>
+        <v>0.58568401119695</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.16759364966573</v>
+        <v>44.93407491973259</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08350783469840456</v>
+        <v>0.08328547581099827</v>
       </c>
       <c r="C7">
-        <v>217.610900574079</v>
+        <v>215.9885451678611</v>
       </c>
       <c r="D7">
-        <v>179.325900574079</v>
+        <v>179.9865451678612</v>
       </c>
       <c r="E7">
-        <v>-40.785</v>
+        <v>-38.502</v>
       </c>
       <c r="F7">
-        <v>11.415</v>
+        <v>13.698</v>
       </c>
       <c r="G7">
         <v>49.7</v>
@@ -1861,28 +1861,28 @@
         <v>25.8</v>
       </c>
       <c r="M7">
-        <v>0.5741745</v>
+        <v>0.6890094000000001</v>
       </c>
       <c r="N7">
-        <v>25.2258255</v>
+        <v>25.1109906</v>
       </c>
       <c r="O7">
-        <v>7.567747649999999</v>
+        <v>7.53329718</v>
       </c>
       <c r="P7">
-        <v>17.65807785</v>
+        <v>17.57769342</v>
       </c>
       <c r="Q7">
-        <v>25.85807785</v>
+        <v>25.77769342</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08604982599832059</v>
+        <v>0.08635412320318964</v>
       </c>
       <c r="T7">
-        <v>0.58568401119695</v>
+        <v>0.590111906302662</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.93407491973259</v>
+        <v>37.44506243311049</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08328547581099827</v>
+        <v>0.08306311692359196</v>
       </c>
       <c r="C8">
-        <v>215.9885451678611</v>
+        <v>214.3710754488678</v>
       </c>
       <c r="D8">
-        <v>179.9865451678612</v>
+        <v>180.6520754488677</v>
       </c>
       <c r="E8">
-        <v>-38.502</v>
+        <v>-36.219</v>
       </c>
       <c r="F8">
-        <v>13.698</v>
+        <v>15.981</v>
       </c>
       <c r="G8">
         <v>49.7</v>
@@ -1943,28 +1943,28 @@
         <v>25.8</v>
       </c>
       <c r="M8">
-        <v>0.6890094</v>
+        <v>0.8038443</v>
       </c>
       <c r="N8">
-        <v>25.1109906</v>
+        <v>24.9961557</v>
       </c>
       <c r="O8">
-        <v>7.53329718</v>
+        <v>7.49884671</v>
       </c>
       <c r="P8">
-        <v>17.57769342</v>
+        <v>17.49730899</v>
       </c>
       <c r="Q8">
-        <v>25.77769342</v>
+        <v>25.69730899</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08635412320318964</v>
+        <v>0.08666496443396984</v>
       </c>
       <c r="T8">
-        <v>0.590111906302662</v>
+        <v>0.5946350249590344</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.44506243311049</v>
+        <v>32.095767799809</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08306311692359195</v>
+        <v>0.08284075803618562</v>
       </c>
       <c r="C9">
-        <v>214.3710754488678</v>
+        <v>212.7585458151758</v>
       </c>
       <c r="D9">
-        <v>180.6520754488678</v>
+        <v>181.3225458151758</v>
       </c>
       <c r="E9">
-        <v>-36.219</v>
+        <v>-33.936</v>
       </c>
       <c r="F9">
-        <v>15.981</v>
+        <v>18.264</v>
       </c>
       <c r="G9">
         <v>49.7</v>
@@ -2025,28 +2025,28 @@
         <v>25.8</v>
       </c>
       <c r="M9">
-        <v>0.8038443000000001</v>
+        <v>0.9186792000000001</v>
       </c>
       <c r="N9">
-        <v>24.9961557</v>
+        <v>24.8813208</v>
       </c>
       <c r="O9">
-        <v>7.49884671</v>
+        <v>7.46439624</v>
       </c>
       <c r="P9">
-        <v>17.49730899</v>
+        <v>17.41692456</v>
       </c>
       <c r="Q9">
-        <v>25.69730899</v>
+        <v>25.61692456</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08666496443396984</v>
+        <v>0.08698256308281047</v>
       </c>
       <c r="T9">
-        <v>0.5946350249590344</v>
+        <v>0.5992564722818496</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.09576779980899</v>
+        <v>28.08379682483287</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08284075803618562</v>
+        <v>0.08261839914877933</v>
       </c>
       <c r="C10">
-        <v>212.7585458151758</v>
+        <v>211.1510114754405</v>
       </c>
       <c r="D10">
-        <v>181.3225458151758</v>
+        <v>181.9980114754405</v>
       </c>
       <c r="E10">
-        <v>-33.936</v>
+        <v>-31.653</v>
       </c>
       <c r="F10">
-        <v>18.264</v>
+        <v>20.547</v>
       </c>
       <c r="G10">
         <v>49.7</v>
@@ -2107,28 +2107,28 @@
         <v>25.8</v>
       </c>
       <c r="M10">
-        <v>0.9186792000000001</v>
+        <v>1.0335141</v>
       </c>
       <c r="N10">
-        <v>24.8813208</v>
+        <v>24.7664859</v>
       </c>
       <c r="O10">
-        <v>7.46439624</v>
+        <v>7.42994577</v>
       </c>
       <c r="P10">
-        <v>17.41692456</v>
+        <v>17.33654013</v>
       </c>
       <c r="Q10">
-        <v>25.61692456</v>
+        <v>25.53654013</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08698256308281047</v>
+        <v>0.08730714192173553</v>
       </c>
       <c r="T10">
-        <v>0.5992564722818496</v>
+        <v>0.603979489875496</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.08379682483287</v>
+        <v>24.963374955407</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08261839914877933</v>
+        <v>0.08239604026137302</v>
       </c>
       <c r="C11">
-        <v>211.1510114754405</v>
+        <v>209.5485284640501</v>
       </c>
       <c r="D11">
-        <v>181.9980114754405</v>
+        <v>182.6785284640501</v>
       </c>
       <c r="E11">
-        <v>-31.653</v>
+        <v>-29.37</v>
       </c>
       <c r="F11">
-        <v>20.547</v>
+        <v>22.83</v>
       </c>
       <c r="G11">
         <v>49.7</v>
@@ -2189,28 +2189,28 @@
         <v>25.8</v>
       </c>
       <c r="M11">
-        <v>1.0335141</v>
+        <v>1.148349</v>
       </c>
       <c r="N11">
-        <v>24.7664859</v>
+        <v>24.651651</v>
       </c>
       <c r="O11">
-        <v>7.42994577</v>
+        <v>7.3954953</v>
       </c>
       <c r="P11">
-        <v>17.33654013</v>
+        <v>17.2561557</v>
       </c>
       <c r="Q11">
-        <v>25.53654013</v>
+        <v>25.4561557</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08730714192173553</v>
+        <v>0.08763893362374781</v>
       </c>
       <c r="T11">
-        <v>0.603979489875496</v>
+        <v>0.6088074634156678</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.963374955407</v>
+        <v>22.4670374598663</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08239604026137302</v>
+        <v>0.08217368137396672</v>
       </c>
       <c r="C12">
-        <v>209.5485284640501</v>
+        <v>207.9511536566208</v>
       </c>
       <c r="D12">
-        <v>182.6785284640501</v>
+        <v>183.3641536566208</v>
       </c>
       <c r="E12">
-        <v>-29.37</v>
+        <v>-27.087</v>
       </c>
       <c r="F12">
-        <v>22.83</v>
+        <v>25.113</v>
       </c>
       <c r="G12">
         <v>49.7</v>
@@ -2271,28 +2271,28 @@
         <v>25.8</v>
       </c>
       <c r="M12">
-        <v>1.148349</v>
+        <v>1.2631839</v>
       </c>
       <c r="N12">
-        <v>24.651651</v>
+        <v>24.5368161</v>
       </c>
       <c r="O12">
-        <v>7.3954953</v>
+        <v>7.361044829999999</v>
       </c>
       <c r="P12">
-        <v>17.2561557</v>
+        <v>17.17577127</v>
       </c>
       <c r="Q12">
-        <v>25.4561557</v>
+        <v>25.37577127</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08763893362374781</v>
+        <v>0.08797818131906372</v>
       </c>
       <c r="T12">
-        <v>0.6088074634156678</v>
+        <v>0.6137439307432593</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.46703745986629</v>
+        <v>20.42457950896936</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08217368137396672</v>
+        <v>0.0819513224865604</v>
       </c>
       <c r="C13">
-        <v>207.9511536566208</v>
+        <v>206.3589447858434</v>
       </c>
       <c r="D13">
-        <v>183.3641536566208</v>
+        <v>184.0549447858434</v>
       </c>
       <c r="E13">
-        <v>-27.087</v>
+        <v>-24.804</v>
       </c>
       <c r="F13">
-        <v>25.113</v>
+        <v>27.396</v>
       </c>
       <c r="G13">
         <v>49.7</v>
@@ -2353,28 +2353,28 @@
         <v>25.8</v>
       </c>
       <c r="M13">
-        <v>1.2631839</v>
+        <v>1.3780188</v>
       </c>
       <c r="N13">
-        <v>24.5368161</v>
+        <v>24.4219812</v>
       </c>
       <c r="O13">
-        <v>7.361044829999999</v>
+        <v>7.32659436</v>
       </c>
       <c r="P13">
-        <v>17.17577127</v>
+        <v>17.09538684</v>
       </c>
       <c r="Q13">
-        <v>25.37577127</v>
+        <v>25.29538684</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08797818131906372</v>
+        <v>0.08832513918927318</v>
       </c>
       <c r="T13">
-        <v>0.6137439307432593</v>
+        <v>0.6187925905101141</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.42457950896936</v>
+        <v>18.72253121655525</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0819513224865604</v>
+        <v>0.0817289635991541</v>
       </c>
       <c r="C14">
-        <v>206.3589447858434</v>
+        <v>204.7719604576878</v>
       </c>
       <c r="D14">
-        <v>184.0549447858434</v>
+        <v>184.7509604576878</v>
       </c>
       <c r="E14">
-        <v>-24.804</v>
+        <v>-22.521</v>
       </c>
       <c r="F14">
-        <v>27.396</v>
+        <v>29.679</v>
       </c>
       <c r="G14">
         <v>49.7</v>
@@ -2435,28 +2435,28 @@
         <v>25.8</v>
       </c>
       <c r="M14">
-        <v>1.3780188</v>
+        <v>1.4928537</v>
       </c>
       <c r="N14">
-        <v>24.4219812</v>
+        <v>24.3071463</v>
       </c>
       <c r="O14">
-        <v>7.32659436</v>
+        <v>7.292143889999999</v>
       </c>
       <c r="P14">
-        <v>17.09538684</v>
+        <v>17.01500241</v>
       </c>
       <c r="Q14">
-        <v>25.29538684</v>
+        <v>25.21500241</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08832513918927318</v>
+        <v>0.08868007310247597</v>
       </c>
       <c r="T14">
-        <v>0.6187925905101141</v>
+        <v>0.6239573114210346</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.72253121655525</v>
+        <v>17.28233650758946</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0817289635991541</v>
+        <v>0.0815066047117478</v>
       </c>
       <c r="C15">
-        <v>204.7719604576878</v>
+        <v>203.1902601679786</v>
       </c>
       <c r="D15">
-        <v>184.7509604576878</v>
+        <v>185.4522601679786</v>
       </c>
       <c r="E15">
-        <v>-22.521</v>
+        <v>-20.238</v>
       </c>
       <c r="F15">
-        <v>29.679</v>
+        <v>31.962</v>
       </c>
       <c r="G15">
         <v>49.7</v>
@@ -2517,28 +2517,28 @@
         <v>25.8</v>
       </c>
       <c r="M15">
-        <v>1.4928537</v>
+        <v>1.6076886</v>
       </c>
       <c r="N15">
-        <v>24.3071463</v>
+        <v>24.1923114</v>
       </c>
       <c r="O15">
-        <v>7.292143889999999</v>
+        <v>7.25769342</v>
       </c>
       <c r="P15">
-        <v>17.01500241</v>
+        <v>16.93461798</v>
       </c>
       <c r="Q15">
-        <v>25.21500241</v>
+        <v>25.13461798</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08868007310247597</v>
+        <v>0.08904326129272999</v>
       </c>
       <c r="T15">
-        <v>0.6239573114210346</v>
+        <v>0.6292421421205812</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.28233650758946</v>
+        <v>16.0478838999045</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0815066047117478</v>
+        <v>0.08128424582434148</v>
       </c>
       <c r="C16">
-        <v>203.1902601679786</v>
+        <v>201.6139043193476</v>
       </c>
       <c r="D16">
-        <v>185.4522601679786</v>
+        <v>186.1589043193476</v>
       </c>
       <c r="E16">
-        <v>-20.238</v>
+        <v>-17.955</v>
       </c>
       <c r="F16">
-        <v>31.962</v>
+        <v>34.245</v>
       </c>
       <c r="G16">
         <v>49.7</v>
@@ -2599,28 +2599,28 @@
         <v>25.8</v>
       </c>
       <c r="M16">
-        <v>1.6076886</v>
+        <v>1.7225235</v>
       </c>
       <c r="N16">
-        <v>24.1923114</v>
+        <v>24.0774765</v>
       </c>
       <c r="O16">
-        <v>7.25769342</v>
+        <v>7.223242949999999</v>
       </c>
       <c r="P16">
-        <v>16.93461798</v>
+        <v>16.85423355</v>
       </c>
       <c r="Q16">
-        <v>25.13461798</v>
+        <v>25.05423355</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08904326129272999</v>
+        <v>0.08941499508746056</v>
       </c>
       <c r="T16">
-        <v>0.6292421421205812</v>
+        <v>0.6346513217777641</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.0478838999045</v>
+        <v>14.9780249732442</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08128424582434148</v>
+        <v>0.08106188693693517</v>
       </c>
       <c r="C17">
-        <v>201.6139043193476</v>
+        <v>200.0429542385764</v>
       </c>
       <c r="D17">
-        <v>186.1589043193476</v>
+        <v>186.8709542385764</v>
       </c>
       <c r="E17">
-        <v>-17.95500000000001</v>
+        <v>-15.672</v>
       </c>
       <c r="F17">
-        <v>34.245</v>
+        <v>36.52800000000001</v>
       </c>
       <c r="G17">
         <v>49.7</v>
@@ -2681,28 +2681,28 @@
         <v>25.8</v>
       </c>
       <c r="M17">
-        <v>1.7225235</v>
+        <v>1.8373584</v>
       </c>
       <c r="N17">
-        <v>24.0774765</v>
+        <v>23.9626416</v>
       </c>
       <c r="O17">
-        <v>7.223242949999999</v>
+        <v>7.18879248</v>
       </c>
       <c r="P17">
-        <v>16.85423355</v>
+        <v>16.77384912</v>
       </c>
       <c r="Q17">
-        <v>25.05423355</v>
+        <v>24.97384912</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08941499508746056</v>
+        <v>0.08979557968682758</v>
       </c>
       <c r="T17">
-        <v>0.6346513217777641</v>
+        <v>0.6401892914267847</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.9780249732442</v>
+        <v>14.04189841241643</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08106188693693517</v>
+        <v>0.08083952804952886</v>
       </c>
       <c r="C18">
-        <v>200.0429542385764</v>
+        <v>198.4774721943391</v>
       </c>
       <c r="D18">
-        <v>186.8709542385764</v>
+        <v>187.5884721943391</v>
       </c>
       <c r="E18">
-        <v>-15.672</v>
+        <v>-13.389</v>
       </c>
       <c r="F18">
-        <v>36.52800000000001</v>
+        <v>38.81100000000001</v>
       </c>
       <c r="G18">
         <v>49.7</v>
@@ -2763,28 +2763,28 @@
         <v>25.8</v>
       </c>
       <c r="M18">
-        <v>1.8373584</v>
+        <v>1.9521933</v>
       </c>
       <c r="N18">
-        <v>23.9626416</v>
+        <v>23.8478067</v>
       </c>
       <c r="O18">
-        <v>7.18879248</v>
+        <v>7.15434201</v>
       </c>
       <c r="P18">
-        <v>16.77384912</v>
+        <v>16.69346469</v>
       </c>
       <c r="Q18">
-        <v>24.97384912</v>
+        <v>24.89346469</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08979557968682758</v>
+        <v>0.09018533499943238</v>
       </c>
       <c r="T18">
-        <v>0.6401892914267847</v>
+        <v>0.6458607061275891</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.04189841241643</v>
+        <v>13.21590438815664</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08083952804952886</v>
+        <v>0.08080616916212253</v>
       </c>
       <c r="C19">
-        <v>198.4774721943391</v>
+        <v>196.3025917923501</v>
       </c>
       <c r="D19">
-        <v>187.5884721943391</v>
+        <v>187.6965917923501</v>
       </c>
       <c r="E19">
-        <v>-13.389</v>
+        <v>-11.10599999999999</v>
       </c>
       <c r="F19">
-        <v>38.81100000000001</v>
+        <v>41.09400000000001</v>
       </c>
       <c r="G19">
         <v>49.7</v>
@@ -2845,45 +2845,45 @@
         <v>25.8</v>
       </c>
       <c r="M19">
-        <v>1.9521933</v>
+        <v>2.1286692</v>
       </c>
       <c r="N19">
-        <v>23.8478067</v>
+        <v>23.6713308</v>
       </c>
       <c r="O19">
-        <v>7.15434201</v>
+        <v>7.10139924</v>
       </c>
       <c r="P19">
-        <v>16.69346469</v>
+        <v>16.56993156</v>
       </c>
       <c r="Q19">
-        <v>24.89346469</v>
+        <v>24.76993156</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09018533499943238</v>
+        <v>0.09058459653917383</v>
       </c>
       <c r="T19">
-        <v>0.6458607061275891</v>
+        <v>0.6516704480162177</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.21590438815664</v>
+        <v>12.12024865112907</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08080616916212255</v>
+        <v>0.08059431027471625</v>
       </c>
       <c r="C20">
-        <v>196.3025917923501</v>
+        <v>194.7091682377298</v>
       </c>
       <c r="D20">
-        <v>187.6965917923501</v>
+        <v>188.3861682377298</v>
       </c>
       <c r="E20">
-        <v>-11.106</v>
+        <v>-8.823</v>
       </c>
       <c r="F20">
-        <v>41.094</v>
+        <v>43.377</v>
       </c>
       <c r="G20">
         <v>49.7</v>
@@ -2927,28 +2927,28 @@
         <v>25.8</v>
       </c>
       <c r="M20">
-        <v>2.1286692</v>
+        <v>2.2469286</v>
       </c>
       <c r="N20">
-        <v>23.6713308</v>
+        <v>23.5530714</v>
       </c>
       <c r="O20">
-        <v>7.10139924</v>
+        <v>7.06592142</v>
       </c>
       <c r="P20">
-        <v>16.56993156</v>
+        <v>16.48714998</v>
       </c>
       <c r="Q20">
-        <v>24.76993156</v>
+        <v>24.68714998</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09058459653917383</v>
+        <v>0.09099371638853856</v>
       </c>
       <c r="T20">
-        <v>0.6516704480162177</v>
+        <v>0.6576236403218496</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.12024865112907</v>
+        <v>11.48234082738544</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08059431027471625</v>
+        <v>0.08038245138730993</v>
       </c>
       <c r="C21">
-        <v>194.7091682377298</v>
+        <v>193.1208302214584</v>
       </c>
       <c r="D21">
-        <v>188.3861682377298</v>
+        <v>189.0808302214584</v>
       </c>
       <c r="E21">
-        <v>-8.823</v>
+        <v>-6.539999999999999</v>
       </c>
       <c r="F21">
-        <v>43.377</v>
+        <v>45.66</v>
       </c>
       <c r="G21">
         <v>49.7</v>
@@ -3009,28 +3009,28 @@
         <v>25.8</v>
       </c>
       <c r="M21">
-        <v>2.2469286</v>
+        <v>2.365188</v>
       </c>
       <c r="N21">
-        <v>23.5530714</v>
+        <v>23.434812</v>
       </c>
       <c r="O21">
-        <v>7.06592142</v>
+        <v>7.0304436</v>
       </c>
       <c r="P21">
-        <v>16.48714998</v>
+        <v>16.4043684</v>
       </c>
       <c r="Q21">
-        <v>24.68714998</v>
+        <v>24.6043684</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09099371638853856</v>
+        <v>0.09141306423413742</v>
       </c>
       <c r="T21">
-        <v>0.6576236403218496</v>
+        <v>0.6637256624351224</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.48234082738544</v>
+        <v>10.90822378601616</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08038245138730993</v>
+        <v>0.08017059249990365</v>
       </c>
       <c r="C22">
-        <v>193.1208302214584</v>
+        <v>191.5376342095457</v>
       </c>
       <c r="D22">
-        <v>189.0808302214584</v>
+        <v>189.7806342095457</v>
       </c>
       <c r="E22">
-        <v>-6.539999999999999</v>
+        <v>-4.256999999999998</v>
       </c>
       <c r="F22">
-        <v>45.66</v>
+        <v>47.943</v>
       </c>
       <c r="G22">
         <v>49.7</v>
@@ -3091,28 +3091,28 @@
         <v>25.8</v>
       </c>
       <c r="M22">
-        <v>2.365188</v>
+        <v>2.4834474</v>
       </c>
       <c r="N22">
-        <v>23.434812</v>
+        <v>23.3165526</v>
       </c>
       <c r="O22">
-        <v>7.0304436</v>
+        <v>6.99496578</v>
       </c>
       <c r="P22">
-        <v>16.4043684</v>
+        <v>16.32158682</v>
       </c>
       <c r="Q22">
-        <v>24.6043684</v>
+        <v>24.52158682</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09141306423413742</v>
+        <v>0.09184302848089068</v>
       </c>
       <c r="T22">
-        <v>0.6637256624351224</v>
+        <v>0.6699821661208831</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.90822378601616</v>
+        <v>10.38878455811063</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08017059249990363</v>
+        <v>0.07995873361249732</v>
       </c>
       <c r="C23">
-        <v>191.5376342095458</v>
+        <v>189.9596375070491</v>
       </c>
       <c r="D23">
-        <v>189.7806342095458</v>
+        <v>190.4856375070491</v>
       </c>
       <c r="E23">
-        <v>-4.257000000000005</v>
+        <v>-1.973999999999997</v>
       </c>
       <c r="F23">
-        <v>47.943</v>
+        <v>50.22600000000001</v>
       </c>
       <c r="G23">
         <v>49.7</v>
@@ -3173,28 +3173,28 @@
         <v>25.8</v>
       </c>
       <c r="M23">
-        <v>2.4834474</v>
+        <v>2.6017068</v>
       </c>
       <c r="N23">
-        <v>23.3165526</v>
+        <v>23.1982932</v>
       </c>
       <c r="O23">
-        <v>6.99496578</v>
+        <v>6.959487960000001</v>
       </c>
       <c r="P23">
-        <v>16.32158682</v>
+        <v>16.23880524</v>
       </c>
       <c r="Q23">
-        <v>24.52158682</v>
+        <v>24.43880524</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09184302848089067</v>
+        <v>0.09228401745191964</v>
       </c>
       <c r="T23">
-        <v>0.669982166120883</v>
+        <v>0.6763990929780734</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.38878455811063</v>
+        <v>9.916567078196513</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07995873361249732</v>
+        <v>0.080020574725091</v>
       </c>
       <c r="C24">
-        <v>189.9596375070491</v>
+        <v>187.4703079598268</v>
       </c>
       <c r="D24">
-        <v>190.4856375070491</v>
+        <v>190.2793079598268</v>
       </c>
       <c r="E24">
-        <v>-1.973999999999997</v>
+        <v>0.3090000000000046</v>
       </c>
       <c r="F24">
-        <v>50.22600000000001</v>
+        <v>52.50900000000001</v>
       </c>
       <c r="G24">
         <v>49.7</v>
@@ -3255,45 +3255,45 @@
         <v>25.8</v>
       </c>
       <c r="M24">
-        <v>2.6017068</v>
+        <v>2.809231500000001</v>
       </c>
       <c r="N24">
-        <v>23.1982932</v>
+        <v>22.9907685</v>
       </c>
       <c r="O24">
-        <v>6.959487960000001</v>
+        <v>6.897230550000001</v>
       </c>
       <c r="P24">
-        <v>16.23880524</v>
+        <v>16.09353795</v>
       </c>
       <c r="Q24">
-        <v>24.43880524</v>
+        <v>24.29353795</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09228401745191964</v>
+        <v>0.09273646068193636</v>
       </c>
       <c r="T24">
-        <v>0.6763990929780734</v>
+        <v>0.6829826932601258</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>9.916567078196513</v>
+        <v>9.18400637327326</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.080020574725091</v>
+        <v>0.0798206158376847</v>
       </c>
       <c r="C25">
-        <v>187.4703079598268</v>
+        <v>185.8560796824511</v>
       </c>
       <c r="D25">
-        <v>190.2793079598268</v>
+        <v>190.9480796824511</v>
       </c>
       <c r="E25">
-        <v>0.3090000000000046</v>
+        <v>2.592000000000006</v>
       </c>
       <c r="F25">
-        <v>52.50900000000001</v>
+        <v>54.79200000000001</v>
       </c>
       <c r="G25">
         <v>49.7</v>
@@ -3337,28 +3337,28 @@
         <v>25.8</v>
       </c>
       <c r="M25">
-        <v>2.809231500000001</v>
+        <v>2.931372000000001</v>
       </c>
       <c r="N25">
-        <v>22.9907685</v>
+        <v>22.868628</v>
       </c>
       <c r="O25">
-        <v>6.897230550000001</v>
+        <v>6.8605884</v>
       </c>
       <c r="P25">
-        <v>16.09353795</v>
+        <v>16.0080396</v>
       </c>
       <c r="Q25">
-        <v>24.29353795</v>
+        <v>24.2080396</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09273646068193636</v>
+        <v>0.09320081031274302</v>
       </c>
       <c r="T25">
-        <v>0.6829826932601258</v>
+        <v>0.6897395461811798</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.18400637327326</v>
+        <v>8.801339441053539</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0798206158376847</v>
+        <v>0.0796206569502784</v>
       </c>
       <c r="C26">
-        <v>185.8560796824511</v>
+        <v>184.2465690291681</v>
       </c>
       <c r="D26">
-        <v>190.9480796824511</v>
+        <v>191.6215690291681</v>
       </c>
       <c r="E26">
-        <v>2.591999999999999</v>
+        <v>4.875</v>
       </c>
       <c r="F26">
-        <v>54.792</v>
+        <v>57.075</v>
       </c>
       <c r="G26">
         <v>49.7</v>
@@ -3419,28 +3419,28 @@
         <v>25.8</v>
       </c>
       <c r="M26">
-        <v>2.931372</v>
+        <v>3.0535125</v>
       </c>
       <c r="N26">
-        <v>22.868628</v>
+        <v>22.7464875</v>
       </c>
       <c r="O26">
-        <v>6.8605884</v>
+        <v>6.82394625</v>
       </c>
       <c r="P26">
-        <v>16.0080396</v>
+        <v>15.92254125</v>
       </c>
       <c r="Q26">
-        <v>24.2080396</v>
+        <v>24.12254125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09320081031274302</v>
+        <v>0.0936775426003712</v>
       </c>
       <c r="T26">
-        <v>0.6897395461811798</v>
+        <v>0.6966765818467952</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.801339441053541</v>
+        <v>8.449285863411399</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0796206569502784</v>
+        <v>0.07942069806287208</v>
       </c>
       <c r="C27">
-        <v>184.2465690291681</v>
+        <v>182.641826094994</v>
       </c>
       <c r="D27">
-        <v>191.6215690291681</v>
+        <v>192.299826094994</v>
       </c>
       <c r="E27">
-        <v>4.875</v>
+        <v>7.158000000000001</v>
       </c>
       <c r="F27">
-        <v>57.075</v>
+        <v>59.358</v>
       </c>
       <c r="G27">
         <v>49.7</v>
@@ -3501,28 +3501,28 @@
         <v>25.8</v>
       </c>
       <c r="M27">
-        <v>3.0535125</v>
+        <v>3.175653</v>
       </c>
       <c r="N27">
-        <v>22.7464875</v>
+        <v>22.624347</v>
       </c>
       <c r="O27">
-        <v>6.82394625</v>
+        <v>6.7873041</v>
       </c>
       <c r="P27">
-        <v>15.92254125</v>
+        <v>15.8370429</v>
       </c>
       <c r="Q27">
-        <v>24.12254125</v>
+        <v>24.0370429</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0936775426003712</v>
+        <v>0.09416715954442173</v>
       </c>
       <c r="T27">
-        <v>0.6966765818467952</v>
+        <v>0.7038011049628324</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.449285863411399</v>
+        <v>8.124313330203268</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07942069806287208</v>
+        <v>0.07922073917546577</v>
       </c>
       <c r="C28">
-        <v>182.641826094994</v>
+        <v>181.0419016867228</v>
       </c>
       <c r="D28">
-        <v>192.299826094994</v>
+        <v>192.9829016867228</v>
       </c>
       <c r="E28">
-        <v>7.158000000000001</v>
+        <v>9.441000000000003</v>
       </c>
       <c r="F28">
-        <v>59.358</v>
+        <v>61.64100000000001</v>
       </c>
       <c r="G28">
         <v>49.7</v>
@@ -3583,28 +3583,28 @@
         <v>25.8</v>
       </c>
       <c r="M28">
-        <v>3.175653</v>
+        <v>3.2977935</v>
       </c>
       <c r="N28">
-        <v>22.624347</v>
+        <v>22.5022065</v>
       </c>
       <c r="O28">
-        <v>6.7873041</v>
+        <v>6.75066195</v>
       </c>
       <c r="P28">
-        <v>15.8370429</v>
+        <v>15.75154455</v>
       </c>
       <c r="Q28">
-        <v>24.0370429</v>
+        <v>23.95154455</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09416715954442173</v>
+        <v>0.09467019065132298</v>
       </c>
       <c r="T28">
-        <v>0.7038011049628324</v>
+        <v>0.711120820493008</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.124313330203268</v>
+        <v>7.823412836492036</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07922073917546577</v>
+        <v>0.07917758028805946</v>
       </c>
       <c r="C29">
-        <v>181.0419016867228</v>
+        <v>178.9069731380535</v>
       </c>
       <c r="D29">
-        <v>192.9829016867228</v>
+        <v>193.1309731380535</v>
       </c>
       <c r="E29">
-        <v>9.441000000000003</v>
+        <v>11.724</v>
       </c>
       <c r="F29">
-        <v>61.64100000000001</v>
+        <v>63.92400000000001</v>
       </c>
       <c r="G29">
         <v>49.7</v>
@@ -3665,45 +3665,45 @@
         <v>25.8</v>
       </c>
       <c r="M29">
-        <v>3.2977935</v>
+        <v>3.471073200000001</v>
       </c>
       <c r="N29">
-        <v>22.5022065</v>
+        <v>22.3289268</v>
       </c>
       <c r="O29">
-        <v>6.75066195</v>
+        <v>6.69867804</v>
       </c>
       <c r="P29">
-        <v>15.75154455</v>
+        <v>15.63024876</v>
       </c>
       <c r="Q29">
-        <v>23.95154455</v>
+        <v>23.83024876</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09467019065132298</v>
+        <v>0.09518719484452703</v>
       </c>
       <c r="T29">
-        <v>0.711120820493008</v>
+        <v>0.7186438614545769</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.823412836492036</v>
+        <v>7.43285967002943</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07917758028805946</v>
+        <v>0.07898322140065316</v>
       </c>
       <c r="C30">
-        <v>178.9069731380535</v>
+        <v>177.2936137938433</v>
       </c>
       <c r="D30">
-        <v>193.1309731380535</v>
+        <v>193.8006137938434</v>
       </c>
       <c r="E30">
-        <v>11.724</v>
+        <v>14.00700000000001</v>
       </c>
       <c r="F30">
-        <v>63.92400000000001</v>
+        <v>66.20700000000001</v>
       </c>
       <c r="G30">
         <v>49.7</v>
@@ -3747,28 +3747,28 @@
         <v>25.8</v>
       </c>
       <c r="M30">
-        <v>3.471073200000001</v>
+        <v>3.5950401</v>
       </c>
       <c r="N30">
-        <v>22.3289268</v>
+        <v>22.2049599</v>
       </c>
       <c r="O30">
-        <v>6.69867804</v>
+        <v>6.66148797</v>
       </c>
       <c r="P30">
-        <v>15.63024876</v>
+        <v>15.54347193</v>
       </c>
       <c r="Q30">
-        <v>23.83024876</v>
+        <v>23.74347193</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09518719484452703</v>
+        <v>0.09571876253613121</v>
       </c>
       <c r="T30">
-        <v>0.7186438614545769</v>
+        <v>0.7263788190629509</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.43285967002943</v>
+        <v>7.176554164166346</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07898322140065316</v>
+        <v>0.07878886251324685</v>
       </c>
       <c r="C31">
-        <v>177.2936137938433</v>
+        <v>175.6849142802818</v>
       </c>
       <c r="D31">
-        <v>193.8006137938434</v>
+        <v>194.4749142802818</v>
       </c>
       <c r="E31">
-        <v>14.00699999999999</v>
+        <v>16.28999999999999</v>
       </c>
       <c r="F31">
-        <v>66.20699999999999</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="G31">
         <v>49.7</v>
@@ -3829,28 +3829,28 @@
         <v>25.8</v>
       </c>
       <c r="M31">
-        <v>3.5950401</v>
+        <v>3.719007</v>
       </c>
       <c r="N31">
-        <v>22.2049599</v>
+        <v>22.080993</v>
       </c>
       <c r="O31">
-        <v>6.66148797</v>
+        <v>6.624297899999999</v>
       </c>
       <c r="P31">
-        <v>15.54347193</v>
+        <v>15.4566951</v>
       </c>
       <c r="Q31">
-        <v>23.74347193</v>
+        <v>23.6566951</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09571876253613121</v>
+        <v>0.09626551787606694</v>
       </c>
       <c r="T31">
-        <v>0.7263788190629509</v>
+        <v>0.7343347754601355</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.176554164166348</v>
+        <v>6.937335692027468</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07878886251324685</v>
+        <v>0.07859450362584053</v>
       </c>
       <c r="C32">
-        <v>175.6849142802818</v>
+        <v>174.0809234067624</v>
       </c>
       <c r="D32">
-        <v>194.4749142802818</v>
+        <v>195.1539234067623</v>
       </c>
       <c r="E32">
-        <v>16.28999999999999</v>
+        <v>18.57299999999999</v>
       </c>
       <c r="F32">
-        <v>68.48999999999999</v>
+        <v>70.773</v>
       </c>
       <c r="G32">
         <v>49.7</v>
@@ -3911,28 +3911,28 @@
         <v>25.8</v>
       </c>
       <c r="M32">
-        <v>3.719007</v>
+        <v>3.8429739</v>
       </c>
       <c r="N32">
-        <v>22.080993</v>
+        <v>21.9570261</v>
       </c>
       <c r="O32">
-        <v>6.624297899999999</v>
+        <v>6.58710783</v>
       </c>
       <c r="P32">
-        <v>15.4566951</v>
+        <v>15.36991827</v>
       </c>
       <c r="Q32">
-        <v>23.6566951</v>
+        <v>23.56991827</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09626551787606694</v>
+        <v>0.09682812119687034</v>
       </c>
       <c r="T32">
-        <v>0.7343347754601355</v>
+        <v>0.7425213392891223</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.937335692027468</v>
+        <v>6.713550669704002</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07859450362584053</v>
+        <v>0.07840014473843422</v>
       </c>
       <c r="C33">
-        <v>174.0809234067624</v>
+        <v>172.4816906667388</v>
       </c>
       <c r="D33">
-        <v>195.1539234067623</v>
+        <v>195.8376906667388</v>
       </c>
       <c r="E33">
-        <v>18.57299999999999</v>
+        <v>20.85600000000001</v>
       </c>
       <c r="F33">
-        <v>70.773</v>
+        <v>73.05600000000001</v>
       </c>
       <c r="G33">
         <v>49.7</v>
@@ -3993,28 +3993,28 @@
         <v>25.8</v>
       </c>
       <c r="M33">
-        <v>3.8429739</v>
+        <v>3.966940800000001</v>
       </c>
       <c r="N33">
-        <v>21.9570261</v>
+        <v>21.8330592</v>
       </c>
       <c r="O33">
-        <v>6.58710783</v>
+        <v>6.54991776</v>
       </c>
       <c r="P33">
-        <v>15.36991827</v>
+        <v>15.28314144</v>
       </c>
       <c r="Q33">
-        <v>23.56991827</v>
+        <v>23.48314144</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09682812119687034</v>
+        <v>0.09740727167416799</v>
       </c>
       <c r="T33">
-        <v>0.7425213392891223</v>
+        <v>0.7509486844071973</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.713550669704002</v>
+        <v>6.503752211275751</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07840014473843422</v>
+        <v>0.07820578585102791</v>
       </c>
       <c r="C34">
-        <v>172.4816906667388</v>
+        <v>170.8872662497514</v>
       </c>
       <c r="D34">
-        <v>195.8376906667388</v>
+        <v>196.5262662497514</v>
       </c>
       <c r="E34">
-        <v>20.85600000000001</v>
+        <v>23.13900000000001</v>
       </c>
       <c r="F34">
-        <v>73.05600000000001</v>
+        <v>75.33900000000001</v>
       </c>
       <c r="G34">
         <v>49.7</v>
@@ -4075,28 +4075,28 @@
         <v>25.8</v>
       </c>
       <c r="M34">
-        <v>3.966940800000001</v>
+        <v>4.090907700000001</v>
       </c>
       <c r="N34">
-        <v>21.8330592</v>
+        <v>21.7090923</v>
       </c>
       <c r="O34">
-        <v>6.54991776</v>
+        <v>6.51272769</v>
       </c>
       <c r="P34">
-        <v>15.28314144</v>
+        <v>15.19636461</v>
       </c>
       <c r="Q34">
-        <v>23.48314144</v>
+        <v>23.39636461</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09740727167416799</v>
+        <v>0.09800371022541482</v>
       </c>
       <c r="T34">
-        <v>0.7509486844071973</v>
+        <v>0.7596275920661103</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.503752211275751</v>
+        <v>6.306668810934062</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07820578585102791</v>
+        <v>0.07801142696362162</v>
       </c>
       <c r="C35">
-        <v>170.8872662497514</v>
+        <v>169.297701053707</v>
       </c>
       <c r="D35">
-        <v>196.5262662497514</v>
+        <v>197.219701053707</v>
       </c>
       <c r="E35">
-        <v>23.13900000000001</v>
+        <v>25.42200000000001</v>
       </c>
       <c r="F35">
-        <v>75.33900000000001</v>
+        <v>77.62200000000001</v>
       </c>
       <c r="G35">
         <v>49.7</v>
@@ -4157,28 +4157,28 @@
         <v>25.8</v>
       </c>
       <c r="M35">
-        <v>4.090907700000001</v>
+        <v>4.214874600000001</v>
       </c>
       <c r="N35">
-        <v>21.7090923</v>
+        <v>21.5851254</v>
       </c>
       <c r="O35">
-        <v>6.51272769</v>
+        <v>6.47553762</v>
       </c>
       <c r="P35">
-        <v>15.19636461</v>
+        <v>15.10958778</v>
       </c>
       <c r="Q35">
-        <v>23.39636461</v>
+        <v>23.30958778</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09800371022541482</v>
+        <v>0.09861822267215398</v>
       </c>
       <c r="T35">
-        <v>0.7596275920661103</v>
+        <v>0.7685694969268084</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.306668810934062</v>
+        <v>6.121178551788942</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07801142696362162</v>
+        <v>0.07806206807621531</v>
       </c>
       <c r="C36">
-        <v>169.297701053707</v>
+        <v>166.8335524150029</v>
       </c>
       <c r="D36">
-        <v>197.219701053707</v>
+        <v>197.0385524150029</v>
       </c>
       <c r="E36">
-        <v>25.42200000000001</v>
+        <v>27.70500000000001</v>
       </c>
       <c r="F36">
-        <v>77.62200000000001</v>
+        <v>79.90500000000002</v>
       </c>
       <c r="G36">
         <v>49.7</v>
@@ -4239,45 +4239,45 @@
         <v>25.8</v>
       </c>
       <c r="M36">
-        <v>4.214874600000001</v>
+        <v>4.418746500000001</v>
       </c>
       <c r="N36">
-        <v>21.5851254</v>
+        <v>21.3812535</v>
       </c>
       <c r="O36">
-        <v>6.47553762</v>
+        <v>6.41437605</v>
       </c>
       <c r="P36">
-        <v>15.10958778</v>
+        <v>14.96687745</v>
       </c>
       <c r="Q36">
-        <v>23.30958778</v>
+        <v>23.16687745</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09861822267215398</v>
+        <v>0.0992516431941774</v>
       </c>
       <c r="T36">
-        <v>0.7685694969268084</v>
+        <v>0.7777865373216819</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.121178551788942</v>
+        <v>5.838759928862177</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07806206807621531</v>
+        <v>0.077874709188809</v>
       </c>
       <c r="C37">
-        <v>166.8335524150029</v>
+        <v>165.2224226526329</v>
       </c>
       <c r="D37">
-        <v>197.0385524150029</v>
+        <v>197.7104226526329</v>
       </c>
       <c r="E37">
-        <v>27.70500000000001</v>
+        <v>29.98800000000001</v>
       </c>
       <c r="F37">
-        <v>79.90500000000002</v>
+        <v>82.18800000000002</v>
       </c>
       <c r="G37">
         <v>49.7</v>
@@ -4321,28 +4321,28 @@
         <v>25.8</v>
       </c>
       <c r="M37">
-        <v>4.418746500000001</v>
+        <v>4.544996400000001</v>
       </c>
       <c r="N37">
-        <v>21.3812535</v>
+        <v>21.2550036</v>
       </c>
       <c r="O37">
-        <v>6.41437605</v>
+        <v>6.37650108</v>
       </c>
       <c r="P37">
-        <v>14.96687745</v>
+        <v>14.87850252</v>
       </c>
       <c r="Q37">
-        <v>23.16687745</v>
+        <v>23.07850252</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0992516431941774</v>
+        <v>0.09990485810751407</v>
       </c>
       <c r="T37">
-        <v>0.7777865373216819</v>
+        <v>0.7872916102288952</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.838759928862177</v>
+        <v>5.67657215306045</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07787470918880901</v>
+        <v>0.0776873503014027</v>
       </c>
       <c r="C38">
-        <v>165.2224226526328</v>
+        <v>163.6158905094842</v>
       </c>
       <c r="D38">
-        <v>197.7104226526328</v>
+        <v>198.3868905094842</v>
       </c>
       <c r="E38">
-        <v>29.988</v>
+        <v>32.271</v>
       </c>
       <c r="F38">
-        <v>82.188</v>
+        <v>84.471</v>
       </c>
       <c r="G38">
         <v>49.7</v>
@@ -4403,28 +4403,28 @@
         <v>25.8</v>
       </c>
       <c r="M38">
-        <v>4.5449964</v>
+        <v>4.6712463</v>
       </c>
       <c r="N38">
-        <v>21.2550036</v>
+        <v>21.1287537</v>
       </c>
       <c r="O38">
-        <v>6.376501080000001</v>
+        <v>6.33862611</v>
       </c>
       <c r="P38">
-        <v>14.87850252</v>
+        <v>14.79012759</v>
       </c>
       <c r="Q38">
-        <v>23.07850252</v>
+        <v>22.99012759</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09990485810751407</v>
+        <v>0.1005788100022265</v>
       </c>
       <c r="T38">
-        <v>0.7872916102288952</v>
+        <v>0.7970984314823691</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.676572153060452</v>
+        <v>5.523151284058818</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0776873503014027</v>
+        <v>0.07749999141399638</v>
       </c>
       <c r="C39">
-        <v>163.6158905094842</v>
+        <v>162.0140033399578</v>
       </c>
       <c r="D39">
-        <v>198.3868905094842</v>
+        <v>199.0680033399578</v>
       </c>
       <c r="E39">
-        <v>32.271</v>
+        <v>34.554</v>
       </c>
       <c r="F39">
-        <v>84.471</v>
+        <v>86.754</v>
       </c>
       <c r="G39">
         <v>49.7</v>
@@ -4485,28 +4485,28 @@
         <v>25.8</v>
       </c>
       <c r="M39">
-        <v>4.6712463</v>
+        <v>4.7974962</v>
       </c>
       <c r="N39">
-        <v>21.1287537</v>
+        <v>21.0025038</v>
       </c>
       <c r="O39">
-        <v>6.33862611</v>
+        <v>6.30075114</v>
       </c>
       <c r="P39">
-        <v>14.79012759</v>
+        <v>14.70175266</v>
       </c>
       <c r="Q39">
-        <v>22.99012759</v>
+        <v>22.90175266</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1005788100022265</v>
+        <v>0.1012745022806393</v>
       </c>
       <c r="T39">
-        <v>0.7970984314823691</v>
+        <v>0.8072216018085359</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.523151284058818</v>
+        <v>5.377805197636216</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07749999141399638</v>
+        <v>0.07731263252659008</v>
       </c>
       <c r="C40">
-        <v>162.0140033399578</v>
+        <v>160.4168091510137</v>
       </c>
       <c r="D40">
-        <v>199.0680033399578</v>
+        <v>199.7538091510137</v>
       </c>
       <c r="E40">
-        <v>34.554</v>
+        <v>36.837</v>
       </c>
       <c r="F40">
-        <v>86.754</v>
+        <v>89.03700000000001</v>
       </c>
       <c r="G40">
         <v>49.7</v>
@@ -4567,28 +4567,28 @@
         <v>25.8</v>
       </c>
       <c r="M40">
-        <v>4.7974962</v>
+        <v>4.923746100000001</v>
       </c>
       <c r="N40">
-        <v>21.0025038</v>
+        <v>20.8762539</v>
       </c>
       <c r="O40">
-        <v>6.30075114</v>
+        <v>6.26287617</v>
       </c>
       <c r="P40">
-        <v>14.70175266</v>
+        <v>14.61337773</v>
       </c>
       <c r="Q40">
-        <v>22.90175266</v>
+        <v>22.81337773</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1012745022806393</v>
+        <v>0.1019930041419509</v>
       </c>
       <c r="T40">
-        <v>0.8072216018085359</v>
+        <v>0.8176766793585114</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.377805197636216</v>
+        <v>5.239912756671186</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07731263252659008</v>
+        <v>0.07712527363918377</v>
       </c>
       <c r="C41">
-        <v>160.4168091510137</v>
+        <v>158.8243566134511</v>
       </c>
       <c r="D41">
-        <v>199.7538091510137</v>
+        <v>200.4443566134511</v>
       </c>
       <c r="E41">
-        <v>36.837</v>
+        <v>39.12</v>
       </c>
       <c r="F41">
-        <v>89.03700000000001</v>
+        <v>91.32000000000001</v>
       </c>
       <c r="G41">
         <v>49.7</v>
@@ -4649,28 +4649,28 @@
         <v>25.8</v>
       </c>
       <c r="M41">
-        <v>4.923746100000001</v>
+        <v>5.049996</v>
       </c>
       <c r="N41">
-        <v>20.8762539</v>
+        <v>20.750004</v>
       </c>
       <c r="O41">
-        <v>6.26287617</v>
+        <v>6.2250012</v>
       </c>
       <c r="P41">
-        <v>14.61337773</v>
+        <v>14.5250028</v>
       </c>
       <c r="Q41">
-        <v>22.81337773</v>
+        <v>22.7250028</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1019930041419509</v>
+        <v>0.1027354560653063</v>
       </c>
       <c r="T41">
-        <v>0.8176766793585114</v>
+        <v>0.8284802594934861</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.239912756671186</v>
+        <v>5.108914937754406</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07712527363918377</v>
+        <v>0.07693791475177747</v>
       </c>
       <c r="C42">
-        <v>158.8243566134511</v>
+        <v>157.2366950734219</v>
       </c>
       <c r="D42">
-        <v>200.4443566134511</v>
+        <v>201.1396950734219</v>
       </c>
       <c r="E42">
-        <v>39.12</v>
+        <v>41.40300000000001</v>
       </c>
       <c r="F42">
-        <v>91.32000000000001</v>
+        <v>93.60300000000001</v>
       </c>
       <c r="G42">
         <v>49.7</v>
@@ -4731,28 +4731,28 @@
         <v>25.8</v>
       </c>
       <c r="M42">
-        <v>5.049996</v>
+        <v>5.176245900000001</v>
       </c>
       <c r="N42">
-        <v>20.750004</v>
+        <v>20.6237541</v>
       </c>
       <c r="O42">
-        <v>6.2250012</v>
+        <v>6.18712623</v>
       </c>
       <c r="P42">
-        <v>14.5250028</v>
+        <v>14.43662787</v>
       </c>
       <c r="Q42">
-        <v>22.7250028</v>
+        <v>22.63662787</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1027354560653063</v>
+        <v>0.1035030758504703</v>
       </c>
       <c r="T42">
-        <v>0.8284802594934861</v>
+        <v>0.8396500626838836</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.108914937754406</v>
+        <v>4.984307256345762</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07693791475177747</v>
+        <v>0.07675055586437116</v>
       </c>
       <c r="C43">
-        <v>157.2366950734219</v>
+        <v>155.6538745641861</v>
       </c>
       <c r="D43">
-        <v>201.1396950734219</v>
+        <v>201.8398745641861</v>
       </c>
       <c r="E43">
-        <v>41.40300000000001</v>
+        <v>43.68600000000001</v>
       </c>
       <c r="F43">
-        <v>93.60300000000001</v>
+        <v>95.88600000000001</v>
       </c>
       <c r="G43">
         <v>49.7</v>
@@ -4813,28 +4813,28 @@
         <v>25.8</v>
       </c>
       <c r="M43">
-        <v>5.176245900000001</v>
+        <v>5.302495800000001</v>
       </c>
       <c r="N43">
-        <v>20.6237541</v>
+        <v>20.4975042</v>
       </c>
       <c r="O43">
-        <v>6.18712623</v>
+        <v>6.149251260000001</v>
       </c>
       <c r="P43">
-        <v>14.43662787</v>
+        <v>14.34825294</v>
       </c>
       <c r="Q43">
-        <v>22.63662787</v>
+        <v>22.54825294</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1035030758504703</v>
+        <v>0.1042971652833985</v>
       </c>
       <c r="T43">
-        <v>0.8396500626838836</v>
+        <v>0.8512050315015363</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.984307256345762</v>
+        <v>4.865633274051815</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07675055586437116</v>
+        <v>0.07656319697696486</v>
       </c>
       <c r="C44">
-        <v>155.6538745641862</v>
+        <v>154.0759458181125</v>
       </c>
       <c r="D44">
-        <v>201.8398745641861</v>
+        <v>202.5449458181125</v>
       </c>
       <c r="E44">
-        <v>43.68599999999999</v>
+        <v>45.96899999999999</v>
       </c>
       <c r="F44">
-        <v>95.886</v>
+        <v>98.169</v>
       </c>
       <c r="G44">
         <v>49.7</v>
@@ -4895,28 +4895,28 @@
         <v>25.8</v>
       </c>
       <c r="M44">
-        <v>5.3024958</v>
+        <v>5.4287457</v>
       </c>
       <c r="N44">
-        <v>20.4975042</v>
+        <v>20.3712543</v>
       </c>
       <c r="O44">
-        <v>6.149251260000001</v>
+        <v>6.11137629</v>
       </c>
       <c r="P44">
-        <v>14.34825294</v>
+        <v>14.25987801</v>
       </c>
       <c r="Q44">
-        <v>22.54825294</v>
+        <v>22.45987801</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1042971652833985</v>
+        <v>0.1051191175034471</v>
       </c>
       <c r="T44">
-        <v>0.8512050315015361</v>
+        <v>0.8631654378215626</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.865633274051816</v>
+        <v>4.752479011864564</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07656319697696486</v>
+        <v>0.07637583808955853</v>
       </c>
       <c r="C45">
-        <v>154.0759458181125</v>
+        <v>152.5029602789324</v>
       </c>
       <c r="D45">
-        <v>202.5449458181125</v>
+        <v>203.2549602789324</v>
       </c>
       <c r="E45">
-        <v>45.96899999999999</v>
+        <v>48.25200000000001</v>
       </c>
       <c r="F45">
-        <v>98.169</v>
+        <v>100.452</v>
       </c>
       <c r="G45">
         <v>49.7</v>
@@ -4977,28 +4977,28 @@
         <v>25.8</v>
       </c>
       <c r="M45">
-        <v>5.4287457</v>
+        <v>5.554995600000001</v>
       </c>
       <c r="N45">
-        <v>20.3712543</v>
+        <v>20.2450044</v>
       </c>
       <c r="O45">
-        <v>6.11137629</v>
+        <v>6.073501319999999</v>
       </c>
       <c r="P45">
-        <v>14.25987801</v>
+        <v>14.17150308</v>
       </c>
       <c r="Q45">
-        <v>22.45987801</v>
+        <v>22.37150308</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1051191175034471</v>
+        <v>0.1059704251599259</v>
       </c>
       <c r="T45">
-        <v>0.8631654378215626</v>
+        <v>0.8755530015101614</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.752479011864564</v>
+        <v>4.644468125231278</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07637583808955853</v>
+        <v>0.07618847920215224</v>
       </c>
       <c r="C46">
-        <v>152.5029602789324</v>
+        <v>150.9349701142513</v>
       </c>
       <c r="D46">
-        <v>203.2549602789324</v>
+        <v>203.9699701142513</v>
       </c>
       <c r="E46">
-        <v>48.25200000000001</v>
+        <v>50.53500000000001</v>
       </c>
       <c r="F46">
-        <v>100.452</v>
+        <v>102.735</v>
       </c>
       <c r="G46">
         <v>49.7</v>
@@ -5059,28 +5059,28 @@
         <v>25.8</v>
       </c>
       <c r="M46">
-        <v>5.554995600000001</v>
+        <v>5.681245500000001</v>
       </c>
       <c r="N46">
-        <v>20.2450044</v>
+        <v>20.1187545</v>
       </c>
       <c r="O46">
-        <v>6.073501319999999</v>
+        <v>6.03562635</v>
       </c>
       <c r="P46">
-        <v>14.17150308</v>
+        <v>14.08312815</v>
       </c>
       <c r="Q46">
-        <v>22.37150308</v>
+        <v>22.28312815</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1059704251599259</v>
+        <v>0.1068526894584586</v>
       </c>
       <c r="T46">
-        <v>0.8755530015101614</v>
+        <v>0.8883910220601638</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.644468125231278</v>
+        <v>4.541257722448361</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07618847920215224</v>
+        <v>0.07680612031474593</v>
       </c>
       <c r="C47">
-        <v>150.9349701142513</v>
+        <v>146.3137165339708</v>
       </c>
       <c r="D47">
-        <v>203.9699701142513</v>
+        <v>201.6317165339708</v>
       </c>
       <c r="E47">
-        <v>50.53500000000001</v>
+        <v>52.81800000000001</v>
       </c>
       <c r="F47">
-        <v>102.735</v>
+        <v>105.018</v>
       </c>
       <c r="G47">
         <v>49.7</v>
@@ -5141,45 +5141,45 @@
         <v>25.8</v>
       </c>
       <c r="M47">
-        <v>5.681245500000001</v>
+        <v>6.070040400000002</v>
       </c>
       <c r="N47">
-        <v>20.1187545</v>
+        <v>19.7299596</v>
       </c>
       <c r="O47">
-        <v>6.03562635</v>
+        <v>5.91898788</v>
       </c>
       <c r="P47">
-        <v>14.08312815</v>
+        <v>13.81097172</v>
       </c>
       <c r="Q47">
-        <v>22.28312815</v>
+        <v>22.01097172</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1068526894584586</v>
+        <v>0.1077676302124924</v>
       </c>
       <c r="T47">
-        <v>0.8883910220601638</v>
+        <v>0.9017045248527588</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.3</v>
       </c>
       <c r="W47">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.541257722448361</v>
+        <v>4.250383572405877</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07680612031474593</v>
+        <v>0.07663626142733962</v>
       </c>
       <c r="C48">
-        <v>146.3137165339708</v>
+        <v>144.6684036584626</v>
       </c>
       <c r="D48">
-        <v>201.6317165339708</v>
+        <v>202.2694036584626</v>
       </c>
       <c r="E48">
-        <v>52.81800000000001</v>
+        <v>55.10100000000001</v>
       </c>
       <c r="F48">
-        <v>105.018</v>
+        <v>107.301</v>
       </c>
       <c r="G48">
         <v>49.7</v>
@@ -5223,28 +5223,28 @@
         <v>25.8</v>
       </c>
       <c r="M48">
-        <v>6.070040400000002</v>
+        <v>6.201997800000002</v>
       </c>
       <c r="N48">
-        <v>19.7299596</v>
+        <v>19.5980022</v>
       </c>
       <c r="O48">
-        <v>5.91898788</v>
+        <v>5.87940066</v>
       </c>
       <c r="P48">
-        <v>13.81097172</v>
+        <v>13.71860154</v>
       </c>
       <c r="Q48">
-        <v>22.01097172</v>
+        <v>21.91860154</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1077676302124924</v>
+        <v>0.1087170970327163</v>
       </c>
       <c r="T48">
-        <v>0.9017045248527588</v>
+        <v>0.9155204239771499</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.250383572405877</v>
+        <v>4.159949879375964</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07663626142733962</v>
+        <v>0.07646640253993331</v>
       </c>
       <c r="C49">
-        <v>144.6684036584626</v>
+        <v>143.027137120748</v>
       </c>
       <c r="D49">
-        <v>202.2694036584626</v>
+        <v>202.911137120748</v>
       </c>
       <c r="E49">
-        <v>55.10100000000001</v>
+        <v>57.38400000000001</v>
       </c>
       <c r="F49">
-        <v>107.301</v>
+        <v>109.584</v>
       </c>
       <c r="G49">
         <v>49.7</v>
@@ -5305,28 +5305,28 @@
         <v>25.8</v>
       </c>
       <c r="M49">
-        <v>6.201997800000002</v>
+        <v>6.333955200000002</v>
       </c>
       <c r="N49">
-        <v>19.5980022</v>
+        <v>19.4660448</v>
       </c>
       <c r="O49">
-        <v>5.87940066</v>
+        <v>5.839813439999999</v>
       </c>
       <c r="P49">
-        <v>13.71860154</v>
+        <v>13.62623136</v>
       </c>
       <c r="Q49">
-        <v>21.91860154</v>
+        <v>21.82623136</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1087170970327163</v>
+        <v>0.1097030818075641</v>
       </c>
       <c r="T49">
-        <v>0.9155204239771499</v>
+        <v>0.9298677038370945</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.159949879375964</v>
+        <v>4.073284256888964</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07646640253993331</v>
+        <v>0.07749704365252699</v>
       </c>
       <c r="C50">
-        <v>143.027137120748</v>
+        <v>136.9117568204134</v>
       </c>
       <c r="D50">
-        <v>202.911137120748</v>
+        <v>199.0787568204134</v>
       </c>
       <c r="E50">
-        <v>57.384</v>
+        <v>59.667</v>
       </c>
       <c r="F50">
-        <v>109.584</v>
+        <v>111.867</v>
       </c>
       <c r="G50">
         <v>49.7</v>
@@ -5387,45 +5387,45 @@
         <v>25.8</v>
       </c>
       <c r="M50">
-        <v>6.333955200000001</v>
+        <v>6.8574471</v>
       </c>
       <c r="N50">
-        <v>19.4660448</v>
+        <v>18.9425529</v>
       </c>
       <c r="O50">
-        <v>5.839813439999999</v>
+        <v>5.682765870000001</v>
       </c>
       <c r="P50">
-        <v>13.62623136</v>
+        <v>13.25978703</v>
       </c>
       <c r="Q50">
-        <v>21.82623136</v>
+        <v>21.45978703</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1097030818075641</v>
+        <v>0.1107277326520137</v>
       </c>
       <c r="T50">
-        <v>0.9298677038370945</v>
+        <v>0.9447776221229193</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.073284256888964</v>
+        <v>3.762333069984602</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07749704365252699</v>
+        <v>0.07735168476512068</v>
       </c>
       <c r="C51">
-        <v>136.9117568204134</v>
+        <v>135.1604733560921</v>
       </c>
       <c r="D51">
-        <v>199.0787568204134</v>
+        <v>199.6104733560921</v>
       </c>
       <c r="E51">
-        <v>59.667</v>
+        <v>61.95</v>
       </c>
       <c r="F51">
-        <v>111.867</v>
+        <v>114.15</v>
       </c>
       <c r="G51">
         <v>49.7</v>
@@ -5469,28 +5469,28 @@
         <v>25.8</v>
       </c>
       <c r="M51">
-        <v>6.8574471</v>
+        <v>6.997395</v>
       </c>
       <c r="N51">
-        <v>18.9425529</v>
+        <v>18.802605</v>
       </c>
       <c r="O51">
-        <v>5.682765870000001</v>
+        <v>5.6407815</v>
       </c>
       <c r="P51">
-        <v>13.25978703</v>
+        <v>13.1618235</v>
       </c>
       <c r="Q51">
-        <v>21.45978703</v>
+        <v>21.3618235</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1107277326520137</v>
+        <v>0.1117933695302414</v>
       </c>
       <c r="T51">
-        <v>0.9447776221229193</v>
+        <v>0.960283937140177</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.762333069984602</v>
+        <v>3.687086408584909</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07735168476512068</v>
+        <v>0.07720632587771438</v>
       </c>
       <c r="C52">
-        <v>135.1604733560921</v>
+        <v>133.4120378060375</v>
       </c>
       <c r="D52">
-        <v>199.6104733560921</v>
+        <v>200.1450378060374</v>
       </c>
       <c r="E52">
-        <v>61.95</v>
+        <v>64.233</v>
       </c>
       <c r="F52">
-        <v>114.15</v>
+        <v>116.433</v>
       </c>
       <c r="G52">
         <v>49.7</v>
@@ -5551,28 +5551,28 @@
         <v>25.8</v>
       </c>
       <c r="M52">
-        <v>6.997395</v>
+        <v>7.1373429</v>
       </c>
       <c r="N52">
-        <v>18.802605</v>
+        <v>18.6626571</v>
       </c>
       <c r="O52">
-        <v>5.6407815</v>
+        <v>5.59879713</v>
       </c>
       <c r="P52">
-        <v>13.1618235</v>
+        <v>13.06385997</v>
       </c>
       <c r="Q52">
-        <v>21.3618235</v>
+        <v>21.26385997</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1117933695302414</v>
+        <v>0.1129025017912538</v>
       </c>
       <c r="T52">
-        <v>0.960283937140177</v>
+        <v>0.9764231629744659</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.687086408584909</v>
+        <v>3.614790596651872</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07720632587771438</v>
+        <v>0.07706096699030807</v>
       </c>
       <c r="C53">
-        <v>133.4120378060375</v>
+        <v>131.6664731121574</v>
       </c>
       <c r="D53">
-        <v>200.1450378060374</v>
+        <v>200.6824731121574</v>
       </c>
       <c r="E53">
-        <v>64.233</v>
+        <v>66.51600000000001</v>
       </c>
       <c r="F53">
-        <v>116.433</v>
+        <v>118.716</v>
       </c>
       <c r="G53">
         <v>49.7</v>
@@ -5633,28 +5633,28 @@
         <v>25.8</v>
       </c>
       <c r="M53">
-        <v>7.1373429</v>
+        <v>7.2772908</v>
       </c>
       <c r="N53">
-        <v>18.6626571</v>
+        <v>18.5227092</v>
       </c>
       <c r="O53">
-        <v>5.59879713</v>
+        <v>5.556812760000001</v>
       </c>
       <c r="P53">
-        <v>13.06385997</v>
+        <v>12.96589644</v>
       </c>
       <c r="Q53">
-        <v>21.26385997</v>
+        <v>21.16589644</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1129025017912538</v>
+        <v>0.1140578478964751</v>
       </c>
       <c r="T53">
-        <v>0.9764231629744659</v>
+        <v>0.9932348565518498</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.614790596651872</v>
+        <v>3.545275392870105</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07706096699030807</v>
+        <v>0.07795440810290176</v>
       </c>
       <c r="C54">
-        <v>131.6664731121574</v>
+        <v>126.1250626319974</v>
       </c>
       <c r="D54">
-        <v>200.6824731121574</v>
+        <v>197.4240626319974</v>
       </c>
       <c r="E54">
-        <v>66.51600000000001</v>
+        <v>68.79900000000001</v>
       </c>
       <c r="F54">
-        <v>118.716</v>
+        <v>120.999</v>
       </c>
       <c r="G54">
         <v>49.7</v>
@@ -5715,45 +5715,45 @@
         <v>25.8</v>
       </c>
       <c r="M54">
-        <v>7.2772908</v>
+        <v>7.756035900000001</v>
       </c>
       <c r="N54">
-        <v>18.5227092</v>
+        <v>18.0439641</v>
       </c>
       <c r="O54">
-        <v>5.556812760000001</v>
+        <v>5.41318923</v>
       </c>
       <c r="P54">
-        <v>12.96589644</v>
+        <v>12.63077487</v>
       </c>
       <c r="Q54">
-        <v>21.16589644</v>
+        <v>20.83077487</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1140578478964751</v>
+        <v>0.1152623576657484</v>
       </c>
       <c r="T54">
-        <v>0.9932348565518498</v>
+        <v>1.010761941345293</v>
       </c>
       <c r="U54">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.3</v>
       </c>
       <c r="W54">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.545275392870105</v>
+        <v>3.326441539549862</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07795440810290176</v>
+        <v>0.07782864921549545</v>
       </c>
       <c r="C55">
-        <v>126.1250626319974</v>
+        <v>124.2942962835021</v>
       </c>
       <c r="D55">
-        <v>197.4240626319974</v>
+        <v>197.8762962835021</v>
       </c>
       <c r="E55">
-        <v>68.79900000000001</v>
+        <v>71.08200000000001</v>
       </c>
       <c r="F55">
-        <v>120.999</v>
+        <v>123.282</v>
       </c>
       <c r="G55">
         <v>49.7</v>
@@ -5797,28 +5797,28 @@
         <v>25.8</v>
       </c>
       <c r="M55">
-        <v>7.756035900000001</v>
+        <v>7.902376200000001</v>
       </c>
       <c r="N55">
-        <v>18.0439641</v>
+        <v>17.8976238</v>
       </c>
       <c r="O55">
-        <v>5.41318923</v>
+        <v>5.369287139999999</v>
       </c>
       <c r="P55">
-        <v>12.63077487</v>
+        <v>12.52833666</v>
       </c>
       <c r="Q55">
-        <v>20.83077487</v>
+        <v>20.72833666</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1152623576657484</v>
+        <v>0.1165192374249901</v>
       </c>
       <c r="T55">
-        <v>1.010761941345293</v>
+        <v>1.029051073303668</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.326441539549862</v>
+        <v>3.264840770298938</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07782864921549545</v>
+        <v>0.07770289032808914</v>
       </c>
       <c r="C56">
-        <v>124.2942962835021</v>
+        <v>122.4656065291737</v>
       </c>
       <c r="D56">
-        <v>197.8762962835021</v>
+        <v>198.3306065291737</v>
       </c>
       <c r="E56">
-        <v>71.08200000000001</v>
+        <v>73.36500000000001</v>
       </c>
       <c r="F56">
-        <v>123.282</v>
+        <v>125.565</v>
       </c>
       <c r="G56">
         <v>49.7</v>
@@ -5879,28 +5879,28 @@
         <v>25.8</v>
       </c>
       <c r="M56">
-        <v>7.902376200000001</v>
+        <v>8.048716500000001</v>
       </c>
       <c r="N56">
-        <v>17.8976238</v>
+        <v>17.7512835</v>
       </c>
       <c r="O56">
-        <v>5.369287139999999</v>
+        <v>5.32538505</v>
       </c>
       <c r="P56">
-        <v>12.52833666</v>
+        <v>12.42589845</v>
       </c>
       <c r="Q56">
-        <v>20.72833666</v>
+        <v>20.62589845</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1165192374249901</v>
+        <v>0.1178319785068647</v>
       </c>
       <c r="T56">
-        <v>1.029051073303668</v>
+        <v>1.048153055571304</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.264840770298938</v>
+        <v>3.205480029020776</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07770289032808914</v>
+        <v>0.07757713144068284</v>
       </c>
       <c r="C57">
-        <v>122.4656065291737</v>
+        <v>120.6390077050751</v>
       </c>
       <c r="D57">
-        <v>198.3306065291737</v>
+        <v>198.7870077050751</v>
       </c>
       <c r="E57">
-        <v>73.36500000000001</v>
+        <v>75.64800000000001</v>
       </c>
       <c r="F57">
-        <v>125.565</v>
+        <v>127.848</v>
       </c>
       <c r="G57">
         <v>49.7</v>
@@ -5961,28 +5961,28 @@
         <v>25.8</v>
       </c>
       <c r="M57">
-        <v>8.048716500000001</v>
+        <v>8.195056800000001</v>
       </c>
       <c r="N57">
-        <v>17.7512835</v>
+        <v>17.6049432</v>
       </c>
       <c r="O57">
-        <v>5.32538505</v>
+        <v>5.28148296</v>
       </c>
       <c r="P57">
-        <v>12.42589845</v>
+        <v>12.32346024</v>
       </c>
       <c r="Q57">
-        <v>20.62589845</v>
+        <v>20.52346024</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1178319785068647</v>
+        <v>0.1192043896379155</v>
       </c>
       <c r="T57">
-        <v>1.048153055571304</v>
+        <v>1.068123309760197</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.205480029020776</v>
+        <v>3.148239314216834</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07757713144068284</v>
+        <v>0.07745137255327651</v>
       </c>
       <c r="C58">
-        <v>120.6390077050751</v>
+        <v>118.8145142795351</v>
       </c>
       <c r="D58">
-        <v>198.7870077050751</v>
+        <v>199.2455142795351</v>
       </c>
       <c r="E58">
-        <v>75.64800000000001</v>
+        <v>77.93100000000003</v>
       </c>
       <c r="F58">
-        <v>127.848</v>
+        <v>130.131</v>
       </c>
       <c r="G58">
         <v>49.7</v>
@@ -6043,28 +6043,28 @@
         <v>25.8</v>
       </c>
       <c r="M58">
-        <v>8.195056800000001</v>
+        <v>8.341397100000002</v>
       </c>
       <c r="N58">
-        <v>17.6049432</v>
+        <v>17.4586029</v>
       </c>
       <c r="O58">
-        <v>5.28148296</v>
+        <v>5.237580869999999</v>
       </c>
       <c r="P58">
-        <v>12.32346024</v>
+        <v>12.22102203</v>
       </c>
       <c r="Q58">
-        <v>20.52346024</v>
+        <v>20.42102203</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1192043896379155</v>
+        <v>0.1206406338448291</v>
       </c>
       <c r="T58">
-        <v>1.068123309760197</v>
+        <v>1.089022412981131</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.148239314216834</v>
+        <v>3.093007045546362</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07745137255327651</v>
+        <v>0.07732561366587022</v>
       </c>
       <c r="C59">
-        <v>118.8145142795351</v>
+        <v>116.992140854677</v>
       </c>
       <c r="D59">
-        <v>199.2455142795351</v>
+        <v>199.706140854677</v>
       </c>
       <c r="E59">
-        <v>77.93100000000003</v>
+        <v>80.21400000000001</v>
       </c>
       <c r="F59">
-        <v>130.131</v>
+        <v>132.414</v>
       </c>
       <c r="G59">
         <v>49.7</v>
@@ -6125,28 +6125,28 @@
         <v>25.8</v>
       </c>
       <c r="M59">
-        <v>8.341397100000002</v>
+        <v>8.487737400000002</v>
       </c>
       <c r="N59">
-        <v>17.4586029</v>
+        <v>17.3122626</v>
       </c>
       <c r="O59">
-        <v>5.237580869999999</v>
+        <v>5.193678779999999</v>
       </c>
       <c r="P59">
-        <v>12.22102203</v>
+        <v>12.11858382</v>
       </c>
       <c r="Q59">
-        <v>20.42102203</v>
+        <v>20.31858382</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1206406338448291</v>
+        <v>0.1221452706330244</v>
       </c>
       <c r="T59">
-        <v>1.089022412981131</v>
+        <v>1.110916711593538</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.093007045546362</v>
+        <v>3.039679337864528</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07732561366587022</v>
+        <v>0.0804212547784639</v>
       </c>
       <c r="C60">
-        <v>116.9921408546771</v>
+        <v>103.9562151993211</v>
       </c>
       <c r="D60">
-        <v>199.706140854677</v>
+        <v>188.9532151993211</v>
       </c>
       <c r="E60">
-        <v>80.21399999999998</v>
+        <v>82.497</v>
       </c>
       <c r="F60">
-        <v>132.414</v>
+        <v>134.697</v>
       </c>
       <c r="G60">
         <v>49.7</v>
@@ -6207,45 +6207,45 @@
         <v>25.8</v>
       </c>
       <c r="M60">
-        <v>8.4877374</v>
+        <v>9.684714300000001</v>
       </c>
       <c r="N60">
-        <v>17.3122626</v>
+        <v>16.1152857</v>
       </c>
       <c r="O60">
-        <v>5.19367878</v>
+        <v>4.83458571</v>
       </c>
       <c r="P60">
-        <v>12.11858382</v>
+        <v>11.28069999</v>
       </c>
       <c r="Q60">
-        <v>20.31858382</v>
+        <v>19.48069999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1221452706330243</v>
+        <v>0.1237233043377168</v>
       </c>
       <c r="T60">
-        <v>1.110916711593538</v>
+        <v>1.133879024772404</v>
       </c>
       <c r="U60">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V60">
         <v>0.3</v>
       </c>
       <c r="W60">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.039679337864529</v>
+        <v>2.663991853636818</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0804212547784639</v>
+        <v>0.0803500958910576</v>
       </c>
       <c r="C61">
-        <v>103.9562151993211</v>
+        <v>101.907371533531</v>
       </c>
       <c r="D61">
-        <v>188.9532151993211</v>
+        <v>189.187371533531</v>
       </c>
       <c r="E61">
-        <v>82.497</v>
+        <v>84.77999999999999</v>
       </c>
       <c r="F61">
-        <v>134.697</v>
+        <v>136.98</v>
       </c>
       <c r="G61">
         <v>49.7</v>
@@ -6289,28 +6289,28 @@
         <v>25.8</v>
       </c>
       <c r="M61">
-        <v>9.684714300000001</v>
+        <v>9.848862</v>
       </c>
       <c r="N61">
-        <v>16.1152857</v>
+        <v>15.951138</v>
       </c>
       <c r="O61">
-        <v>4.83458571</v>
+        <v>4.7853414</v>
       </c>
       <c r="P61">
-        <v>11.28069999</v>
+        <v>11.1657966</v>
       </c>
       <c r="Q61">
-        <v>19.48069999</v>
+        <v>19.3657966</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1237233043377168</v>
+        <v>0.125380239727644</v>
       </c>
       <c r="T61">
-        <v>1.133879024772404</v>
+        <v>1.157989453610213</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.663991853636818</v>
+        <v>2.619591989409538</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0803500958910576</v>
+        <v>0.0802789370036513</v>
       </c>
       <c r="C62">
-        <v>101.907371533531</v>
+        <v>99.85910893453072</v>
       </c>
       <c r="D62">
-        <v>189.187371533531</v>
+        <v>189.4221089345307</v>
       </c>
       <c r="E62">
-        <v>84.77999999999999</v>
+        <v>87.063</v>
       </c>
       <c r="F62">
-        <v>136.98</v>
+        <v>139.263</v>
       </c>
       <c r="G62">
         <v>49.7</v>
@@ -6371,28 +6371,28 @@
         <v>25.8</v>
       </c>
       <c r="M62">
-        <v>9.848862</v>
+        <v>10.0130097</v>
       </c>
       <c r="N62">
-        <v>15.951138</v>
+        <v>15.7869903</v>
       </c>
       <c r="O62">
-        <v>4.7853414</v>
+        <v>4.736097089999999</v>
       </c>
       <c r="P62">
-        <v>11.1657966</v>
+        <v>11.05089321</v>
       </c>
       <c r="Q62">
-        <v>19.3657966</v>
+        <v>19.25089321</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.125380239727644</v>
+        <v>0.1271221461632084</v>
       </c>
       <c r="T62">
-        <v>1.157989453610213</v>
+        <v>1.183336314696116</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.619591989409538</v>
+        <v>2.576647858435611</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0802789370036513</v>
+        <v>0.08020777811624499</v>
       </c>
       <c r="C63">
-        <v>99.85910893453072</v>
+        <v>97.81142956791228</v>
       </c>
       <c r="D63">
-        <v>189.4221089345307</v>
+        <v>189.6574295679123</v>
       </c>
       <c r="E63">
-        <v>87.063</v>
+        <v>89.34599999999999</v>
       </c>
       <c r="F63">
-        <v>139.263</v>
+        <v>141.546</v>
       </c>
       <c r="G63">
         <v>49.7</v>
@@ -6453,28 +6453,28 @@
         <v>25.8</v>
       </c>
       <c r="M63">
-        <v>10.0130097</v>
+        <v>10.1771574</v>
       </c>
       <c r="N63">
-        <v>15.7869903</v>
+        <v>15.6228426</v>
       </c>
       <c r="O63">
-        <v>4.736097089999999</v>
+        <v>4.68685278</v>
       </c>
       <c r="P63">
-        <v>11.05089321</v>
+        <v>10.93598982</v>
       </c>
       <c r="Q63">
-        <v>19.25089321</v>
+        <v>19.13598982</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1271221461632084</v>
+        <v>0.1289557318848552</v>
       </c>
       <c r="T63">
-        <v>1.183336314696116</v>
+        <v>1.210017221102328</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.576647858435611</v>
+        <v>2.53508902200923</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08020777811624499</v>
+        <v>0.08185651922883869</v>
       </c>
       <c r="C64">
-        <v>97.81142956791228</v>
+        <v>90.22205043919911</v>
       </c>
       <c r="D64">
-        <v>189.6574295679123</v>
+        <v>184.3510504391991</v>
       </c>
       <c r="E64">
-        <v>89.34599999999999</v>
+        <v>91.629</v>
       </c>
       <c r="F64">
-        <v>141.546</v>
+        <v>143.829</v>
       </c>
       <c r="G64">
         <v>49.7</v>
@@ -6535,45 +6535,45 @@
         <v>25.8</v>
       </c>
       <c r="M64">
-        <v>10.1771574</v>
+        <v>10.9022382</v>
       </c>
       <c r="N64">
-        <v>15.6228426</v>
+        <v>14.8977618</v>
       </c>
       <c r="O64">
-        <v>4.68685278</v>
+        <v>4.469328539999999</v>
       </c>
       <c r="P64">
-        <v>10.93598982</v>
+        <v>10.42843326</v>
       </c>
       <c r="Q64">
-        <v>19.13598982</v>
+        <v>18.62843326</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1289557318848552</v>
+        <v>0.1308884303482127</v>
       </c>
       <c r="T64">
-        <v>1.210017221102328</v>
+        <v>1.238140338665634</v>
       </c>
       <c r="U64">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
         <v>0.3</v>
       </c>
       <c r="W64">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.53508902200923</v>
+        <v>2.366486544019924</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08185651922883869</v>
+        <v>0.08181266034143236</v>
       </c>
       <c r="C65">
-        <v>90.22205043919911</v>
+        <v>88.0763605540302</v>
       </c>
       <c r="D65">
-        <v>184.3510504391991</v>
+        <v>184.4883605540302</v>
       </c>
       <c r="E65">
-        <v>91.629</v>
+        <v>93.91200000000002</v>
       </c>
       <c r="F65">
-        <v>143.829</v>
+        <v>146.112</v>
       </c>
       <c r="G65">
         <v>49.7</v>
@@ -6617,28 +6617,28 @@
         <v>25.8</v>
       </c>
       <c r="M65">
-        <v>10.9022382</v>
+        <v>11.0752896</v>
       </c>
       <c r="N65">
-        <v>14.8977618</v>
+        <v>14.7247104</v>
       </c>
       <c r="O65">
-        <v>4.469328539999999</v>
+        <v>4.417413119999999</v>
       </c>
       <c r="P65">
-        <v>10.42843326</v>
+        <v>10.30729728</v>
       </c>
       <c r="Q65">
-        <v>18.62843326</v>
+        <v>18.50729728</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1308884303482127</v>
+        <v>0.1329285009484233</v>
       </c>
       <c r="T65">
-        <v>1.238140338665634</v>
+        <v>1.267825851649123</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.366486544019924</v>
+        <v>2.329510191769613</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08181266034143236</v>
+        <v>0.08176880145402605</v>
       </c>
       <c r="C66">
-        <v>88.0763605540302</v>
+        <v>85.93087536659559</v>
       </c>
       <c r="D66">
-        <v>184.4883605540302</v>
+        <v>184.6258753665956</v>
       </c>
       <c r="E66">
-        <v>93.91200000000002</v>
+        <v>96.19500000000001</v>
       </c>
       <c r="F66">
-        <v>146.112</v>
+        <v>148.395</v>
       </c>
       <c r="G66">
         <v>49.7</v>
@@ -6699,28 +6699,28 @@
         <v>25.8</v>
       </c>
       <c r="M66">
-        <v>11.0752896</v>
+        <v>11.248341</v>
       </c>
       <c r="N66">
-        <v>14.7247104</v>
+        <v>14.551659</v>
       </c>
       <c r="O66">
-        <v>4.417413119999999</v>
+        <v>4.3654977</v>
       </c>
       <c r="P66">
-        <v>10.30729728</v>
+        <v>10.1861613</v>
       </c>
       <c r="Q66">
-        <v>18.50729728</v>
+        <v>18.3861613</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1329285009484233</v>
+        <v>0.135085147011503</v>
       </c>
       <c r="T66">
-        <v>1.267825851649123</v>
+        <v>1.299207679660239</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.329510191769613</v>
+        <v>2.293671573434696</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08176880145402605</v>
+        <v>0.08172494256661975</v>
       </c>
       <c r="C67">
-        <v>85.93087536659559</v>
+        <v>83.78559533497238</v>
       </c>
       <c r="D67">
-        <v>184.6258753665956</v>
+        <v>184.7635953349724</v>
       </c>
       <c r="E67">
-        <v>96.19500000000001</v>
+        <v>98.47800000000002</v>
       </c>
       <c r="F67">
-        <v>148.395</v>
+        <v>150.678</v>
       </c>
       <c r="G67">
         <v>49.7</v>
@@ -6781,28 +6781,28 @@
         <v>25.8</v>
       </c>
       <c r="M67">
-        <v>11.248341</v>
+        <v>11.4213924</v>
       </c>
       <c r="N67">
-        <v>14.551659</v>
+        <v>14.3786076</v>
       </c>
       <c r="O67">
-        <v>4.3654977</v>
+        <v>4.313582279999999</v>
       </c>
       <c r="P67">
-        <v>10.1861613</v>
+        <v>10.06502532</v>
       </c>
       <c r="Q67">
-        <v>18.3861613</v>
+        <v>18.26502532</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.135085147011503</v>
+        <v>0.1373686546077051</v>
       </c>
       <c r="T67">
-        <v>1.299207679660239</v>
+        <v>1.332435497554363</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.293671573434696</v>
+        <v>2.2589189738372</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08172494256661975</v>
+        <v>0.08168108367921345</v>
       </c>
       <c r="C68">
-        <v>83.78559533497238</v>
+        <v>81.6405209186056</v>
       </c>
       <c r="D68">
-        <v>184.7635953349724</v>
+        <v>184.9015209186056</v>
       </c>
       <c r="E68">
-        <v>98.47800000000002</v>
+        <v>100.761</v>
       </c>
       <c r="F68">
-        <v>150.678</v>
+        <v>152.961</v>
       </c>
       <c r="G68">
         <v>49.7</v>
@@ -6863,28 +6863,28 @@
         <v>25.8</v>
       </c>
       <c r="M68">
-        <v>11.4213924</v>
+        <v>11.5944438</v>
       </c>
       <c r="N68">
-        <v>14.3786076</v>
+        <v>14.2055562</v>
       </c>
       <c r="O68">
-        <v>4.313582279999999</v>
+        <v>4.261666859999999</v>
       </c>
       <c r="P68">
-        <v>10.06502532</v>
+        <v>9.943889339999998</v>
       </c>
       <c r="Q68">
-        <v>18.26502532</v>
+        <v>18.14388934</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1373686546077051</v>
+        <v>0.1397905566036771</v>
       </c>
       <c r="T68">
-        <v>1.332435497554363</v>
+        <v>1.367677122593586</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.2589189738372</v>
+        <v>2.225203765272465</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08168108367921345</v>
+        <v>0.08163722479180713</v>
       </c>
       <c r="C69">
-        <v>81.6405209186056</v>
+        <v>79.49565257831318</v>
       </c>
       <c r="D69">
-        <v>184.9015209186056</v>
+        <v>185.0396525783132</v>
       </c>
       <c r="E69">
-        <v>100.761</v>
+        <v>103.044</v>
       </c>
       <c r="F69">
-        <v>152.961</v>
+        <v>155.244</v>
       </c>
       <c r="G69">
         <v>49.7</v>
@@ -6945,28 +6945,28 @@
         <v>25.8</v>
       </c>
       <c r="M69">
-        <v>11.5944438</v>
+        <v>11.7674952</v>
       </c>
       <c r="N69">
-        <v>14.2055562</v>
+        <v>14.0325048</v>
       </c>
       <c r="O69">
-        <v>4.261666859999999</v>
+        <v>4.209751439999999</v>
       </c>
       <c r="P69">
-        <v>9.943889339999998</v>
+        <v>9.82275336</v>
       </c>
       <c r="Q69">
-        <v>18.14388934</v>
+        <v>18.02275336</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1397905566036771</v>
+        <v>0.1423638274743973</v>
       </c>
       <c r="T69">
-        <v>1.367677122593586</v>
+        <v>1.405121349197759</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.225203765272465</v>
+        <v>2.192480180489047</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08163722479180713</v>
+        <v>0.08159336590440083</v>
       </c>
       <c r="C70">
-        <v>79.49565257831318</v>
+        <v>77.35099077629096</v>
       </c>
       <c r="D70">
-        <v>185.0396525783132</v>
+        <v>185.177990776291</v>
       </c>
       <c r="E70">
-        <v>103.044</v>
+        <v>105.327</v>
       </c>
       <c r="F70">
-        <v>155.244</v>
+        <v>157.527</v>
       </c>
       <c r="G70">
         <v>49.7</v>
@@ -7027,28 +7027,28 @@
         <v>25.8</v>
       </c>
       <c r="M70">
-        <v>11.7674952</v>
+        <v>11.9405466</v>
       </c>
       <c r="N70">
-        <v>14.0325048</v>
+        <v>13.8594534</v>
       </c>
       <c r="O70">
-        <v>4.209751439999999</v>
+        <v>4.15783602</v>
       </c>
       <c r="P70">
-        <v>9.82275336</v>
+        <v>9.701617379999998</v>
       </c>
       <c r="Q70">
-        <v>18.02275336</v>
+        <v>17.90161738</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1423638274743973</v>
+        <v>0.1451031158206479</v>
       </c>
       <c r="T70">
-        <v>1.405121349197759</v>
+        <v>1.444981332357041</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.192480180489047</v>
+        <v>2.160705105409495</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08159336590440083</v>
+        <v>0.08154950701699452</v>
       </c>
       <c r="C71">
-        <v>77.35099077629096</v>
+        <v>75.2065359761182</v>
       </c>
       <c r="D71">
-        <v>185.177990776291</v>
+        <v>185.3165359761182</v>
       </c>
       <c r="E71">
-        <v>105.327</v>
+        <v>107.61</v>
       </c>
       <c r="F71">
-        <v>157.527</v>
+        <v>159.81</v>
       </c>
       <c r="G71">
         <v>49.7</v>
@@ -7109,28 +7109,28 @@
         <v>25.8</v>
       </c>
       <c r="M71">
-        <v>11.9405466</v>
+        <v>12.113598</v>
       </c>
       <c r="N71">
-        <v>13.8594534</v>
+        <v>13.686402</v>
       </c>
       <c r="O71">
-        <v>4.15783602</v>
+        <v>4.105920599999999</v>
       </c>
       <c r="P71">
-        <v>9.701617379999998</v>
+        <v>9.580481399999998</v>
       </c>
       <c r="Q71">
-        <v>17.90161738</v>
+        <v>17.7804814</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1451031158206479</v>
+        <v>0.1480250233899817</v>
       </c>
       <c r="T71">
-        <v>1.444981332357041</v>
+        <v>1.487498647726941</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.160705105409495</v>
+        <v>2.129837889617932</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08154950701699452</v>
+        <v>0.08150564812958822</v>
       </c>
       <c r="C72">
-        <v>75.2065359761182</v>
+        <v>73.0622886427625</v>
       </c>
       <c r="D72">
-        <v>185.3165359761182</v>
+        <v>185.4552886427625</v>
       </c>
       <c r="E72">
-        <v>107.61</v>
+        <v>109.893</v>
       </c>
       <c r="F72">
-        <v>159.81</v>
+        <v>162.093</v>
       </c>
       <c r="G72">
         <v>49.7</v>
@@ -7191,28 +7191,28 @@
         <v>25.8</v>
       </c>
       <c r="M72">
-        <v>12.113598</v>
+        <v>12.2866494</v>
       </c>
       <c r="N72">
-        <v>13.686402</v>
+        <v>13.5133506</v>
       </c>
       <c r="O72">
-        <v>4.105920599999999</v>
+        <v>4.05400518</v>
       </c>
       <c r="P72">
-        <v>9.580481399999998</v>
+        <v>9.459345419999998</v>
       </c>
       <c r="Q72">
-        <v>17.7804814</v>
+        <v>17.65934542</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1480250233899817</v>
+        <v>0.1511484418261663</v>
       </c>
       <c r="T72">
-        <v>1.487498647726941</v>
+        <v>1.532948191743042</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.129837889617932</v>
+        <v>2.099840172862749</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08150564812958822</v>
+        <v>0.08146178924218191</v>
       </c>
       <c r="C73">
-        <v>73.06228864276252</v>
+        <v>70.91824924258489</v>
       </c>
       <c r="D73">
-        <v>185.4552886427625</v>
+        <v>185.5942492425849</v>
       </c>
       <c r="E73">
-        <v>109.893</v>
+        <v>112.176</v>
       </c>
       <c r="F73">
-        <v>162.093</v>
+        <v>164.376</v>
       </c>
       <c r="G73">
         <v>49.7</v>
@@ -7273,28 +7273,28 @@
         <v>25.8</v>
       </c>
       <c r="M73">
-        <v>12.2866494</v>
+        <v>12.4597008</v>
       </c>
       <c r="N73">
-        <v>13.5133506</v>
+        <v>13.3402992</v>
       </c>
       <c r="O73">
-        <v>4.05400518</v>
+        <v>4.00208976</v>
       </c>
       <c r="P73">
-        <v>9.459345420000002</v>
+        <v>9.33820944</v>
       </c>
       <c r="Q73">
-        <v>17.65934542</v>
+        <v>17.53820944</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1511484418261662</v>
+        <v>0.1544949615792211</v>
       </c>
       <c r="T73">
-        <v>1.532948191743041</v>
+        <v>1.581644131760292</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.09984017286275</v>
+        <v>2.070675726017433</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08146178924218191</v>
+        <v>0.0814179303547756</v>
       </c>
       <c r="C74">
-        <v>70.91824924258489</v>
+        <v>68.77441824334534</v>
       </c>
       <c r="D74">
-        <v>185.5942492425849</v>
+        <v>185.7334182433453</v>
       </c>
       <c r="E74">
-        <v>112.176</v>
+        <v>114.459</v>
       </c>
       <c r="F74">
-        <v>164.376</v>
+        <v>166.659</v>
       </c>
       <c r="G74">
         <v>49.7</v>
@@ -7355,28 +7355,28 @@
         <v>25.8</v>
       </c>
       <c r="M74">
-        <v>12.4597008</v>
+        <v>12.6327522</v>
       </c>
       <c r="N74">
-        <v>13.3402992</v>
+        <v>13.1672478</v>
       </c>
       <c r="O74">
-        <v>4.00208976</v>
+        <v>3.95017434</v>
       </c>
       <c r="P74">
-        <v>9.33820944</v>
+        <v>9.21707346</v>
       </c>
       <c r="Q74">
-        <v>17.53820944</v>
+        <v>17.41707346</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1544949615792211</v>
+        <v>0.1580893716843541</v>
       </c>
       <c r="T74">
-        <v>1.581644131760292</v>
+        <v>1.633947178445486</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.070675726017433</v>
+        <v>2.042310305113086</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0814179303547756</v>
+        <v>0.08137407146736929</v>
       </c>
       <c r="C75">
-        <v>68.77441824334534</v>
+        <v>66.6307961142079</v>
       </c>
       <c r="D75">
-        <v>185.7334182433453</v>
+        <v>185.8727961142079</v>
       </c>
       <c r="E75">
-        <v>114.459</v>
+        <v>116.742</v>
       </c>
       <c r="F75">
-        <v>166.659</v>
+        <v>168.942</v>
       </c>
       <c r="G75">
         <v>49.7</v>
@@ -7437,28 +7437,28 @@
         <v>25.8</v>
       </c>
       <c r="M75">
-        <v>12.6327522</v>
+        <v>12.8058036</v>
       </c>
       <c r="N75">
-        <v>13.1672478</v>
+        <v>12.9941964</v>
       </c>
       <c r="O75">
-        <v>3.95017434</v>
+        <v>3.89825892</v>
       </c>
       <c r="P75">
-        <v>9.21707346</v>
+        <v>9.09593748</v>
       </c>
       <c r="Q75">
-        <v>17.41707346</v>
+        <v>17.29593748</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1580893716843541</v>
+        <v>0.1619602748744972</v>
       </c>
       <c r="T75">
-        <v>1.633947178445486</v>
+        <v>1.690273536414158</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.042310305113086</v>
+        <v>2.014711517206152</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08137407146736929</v>
+        <v>0.08878521257996297</v>
       </c>
       <c r="C76">
-        <v>66.6307961142079</v>
+        <v>43.43082047017305</v>
       </c>
       <c r="D76">
-        <v>185.8727961142079</v>
+        <v>164.9558204701731</v>
       </c>
       <c r="E76">
-        <v>116.742</v>
+        <v>119.025</v>
       </c>
       <c r="F76">
-        <v>168.942</v>
+        <v>171.225</v>
       </c>
       <c r="G76">
         <v>49.7</v>
@@ -7519,45 +7519,45 @@
         <v>25.8</v>
       </c>
       <c r="M76">
-        <v>12.8058036</v>
+        <v>15.41025</v>
       </c>
       <c r="N76">
-        <v>12.9941964</v>
+        <v>10.38975</v>
       </c>
       <c r="O76">
-        <v>3.89825892</v>
+        <v>3.116925</v>
       </c>
       <c r="P76">
-        <v>9.09593748</v>
+        <v>7.272824999999999</v>
       </c>
       <c r="Q76">
-        <v>17.29593748</v>
+        <v>15.472825</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1619602748744972</v>
+        <v>0.1661408503198519</v>
       </c>
       <c r="T76">
-        <v>1.690273536414158</v>
+        <v>1.751106003020323</v>
       </c>
       <c r="U76">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V76">
         <v>0.3</v>
       </c>
       <c r="W76">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.014711517206152</v>
+        <v>1.674210347009295</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08878521257996297</v>
+        <v>0.08884075369255667</v>
       </c>
       <c r="C77">
-        <v>43.43082047017305</v>
+        <v>41.00882069954017</v>
       </c>
       <c r="D77">
-        <v>164.9558204701731</v>
+        <v>164.8168206995402</v>
       </c>
       <c r="E77">
-        <v>119.025</v>
+        <v>121.308</v>
       </c>
       <c r="F77">
-        <v>171.225</v>
+        <v>173.508</v>
       </c>
       <c r="G77">
         <v>49.7</v>
@@ -7601,28 +7601,28 @@
         <v>25.8</v>
       </c>
       <c r="M77">
-        <v>15.41025</v>
+        <v>15.61572</v>
       </c>
       <c r="N77">
-        <v>10.38975</v>
+        <v>10.18428</v>
       </c>
       <c r="O77">
-        <v>3.116925</v>
+        <v>3.055284</v>
       </c>
       <c r="P77">
-        <v>7.272824999999999</v>
+        <v>7.128996000000001</v>
       </c>
       <c r="Q77">
-        <v>15.472825</v>
+        <v>15.328996</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1661408503198519</v>
+        <v>0.1706698070523195</v>
       </c>
       <c r="T77">
-        <v>1.751106003020323</v>
+        <v>1.817007841843668</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.674210347009295</v>
+        <v>1.652181263496016</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08884075369255667</v>
+        <v>0.08889629480515036</v>
       </c>
       <c r="C78">
-        <v>41.00882069954017</v>
+        <v>38.58705498756765</v>
       </c>
       <c r="D78">
-        <v>164.8168206995402</v>
+        <v>164.6780549875677</v>
       </c>
       <c r="E78">
-        <v>121.308</v>
+        <v>123.591</v>
       </c>
       <c r="F78">
-        <v>173.508</v>
+        <v>175.791</v>
       </c>
       <c r="G78">
         <v>49.7</v>
@@ -7683,28 +7683,28 @@
         <v>25.8</v>
       </c>
       <c r="M78">
-        <v>15.61572</v>
+        <v>15.82119</v>
       </c>
       <c r="N78">
-        <v>10.18428</v>
+        <v>9.978809999999999</v>
       </c>
       <c r="O78">
-        <v>3.055284</v>
+        <v>2.993643</v>
       </c>
       <c r="P78">
-        <v>7.128996000000001</v>
+        <v>6.985167</v>
       </c>
       <c r="Q78">
-        <v>15.328996</v>
+        <v>15.185167</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1706698070523195</v>
+        <v>0.1755925861093494</v>
       </c>
       <c r="T78">
-        <v>1.817007841843668</v>
+        <v>1.888640275347305</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.652181263496016</v>
+        <v>1.630724363970093</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08889629480515036</v>
+        <v>0.08895183591774405</v>
       </c>
       <c r="C79">
-        <v>38.58705498756765</v>
+        <v>36.16552274356366</v>
       </c>
       <c r="D79">
-        <v>164.6780549875677</v>
+        <v>164.5395227435637</v>
       </c>
       <c r="E79">
-        <v>123.591</v>
+        <v>125.874</v>
       </c>
       <c r="F79">
-        <v>175.791</v>
+        <v>178.074</v>
       </c>
       <c r="G79">
         <v>49.7</v>
@@ -7765,28 +7765,28 @@
         <v>25.8</v>
       </c>
       <c r="M79">
-        <v>15.82119</v>
+        <v>16.02666</v>
       </c>
       <c r="N79">
-        <v>9.978809999999999</v>
+        <v>9.773340000000001</v>
       </c>
       <c r="O79">
-        <v>2.993643</v>
+        <v>2.932002</v>
       </c>
       <c r="P79">
-        <v>6.985167</v>
+        <v>6.841338</v>
       </c>
       <c r="Q79">
-        <v>15.185167</v>
+        <v>15.041338</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1755925861093494</v>
+        <v>0.1809628905352003</v>
       </c>
       <c r="T79">
-        <v>1.888640275347305</v>
+        <v>1.966784748260363</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.630724363970093</v>
+        <v>1.609817641355092</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08895183591774405</v>
+        <v>0.08900737703033774</v>
       </c>
       <c r="C80">
-        <v>36.16552274356366</v>
+        <v>33.74422337882191</v>
       </c>
       <c r="D80">
-        <v>164.5395227435637</v>
+        <v>164.401223378822</v>
       </c>
       <c r="E80">
-        <v>125.874</v>
+        <v>128.157</v>
       </c>
       <c r="F80">
-        <v>178.074</v>
+        <v>180.357</v>
       </c>
       <c r="G80">
         <v>49.7</v>
@@ -7847,28 +7847,28 @@
         <v>25.8</v>
       </c>
       <c r="M80">
-        <v>16.02666</v>
+        <v>16.23213</v>
       </c>
       <c r="N80">
-        <v>9.773340000000001</v>
+        <v>9.567869999999999</v>
       </c>
       <c r="O80">
-        <v>2.932002</v>
+        <v>2.870360999999999</v>
       </c>
       <c r="P80">
-        <v>6.841338</v>
+        <v>6.697509</v>
       </c>
       <c r="Q80">
-        <v>15.041338</v>
+        <v>14.897509</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1809628905352003</v>
+        <v>0.1868446525254178</v>
       </c>
       <c r="T80">
-        <v>1.966784748260363</v>
+        <v>2.052371551927045</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.609817641355092</v>
+        <v>1.589440202856926</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08900737703033774</v>
+        <v>0.08906291814293144</v>
       </c>
       <c r="C81">
-        <v>33.74422337882191</v>
+        <v>31.32315630661415</v>
       </c>
       <c r="D81">
-        <v>164.401223378822</v>
+        <v>164.2631563066142</v>
       </c>
       <c r="E81">
-        <v>128.157</v>
+        <v>130.44</v>
       </c>
       <c r="F81">
-        <v>180.357</v>
+        <v>182.64</v>
       </c>
       <c r="G81">
         <v>49.7</v>
@@ -7929,28 +7929,28 @@
         <v>25.8</v>
       </c>
       <c r="M81">
-        <v>16.23213</v>
+        <v>16.4376</v>
       </c>
       <c r="N81">
-        <v>9.567869999999999</v>
+        <v>9.362400000000001</v>
       </c>
       <c r="O81">
-        <v>2.870360999999999</v>
+        <v>2.80872</v>
       </c>
       <c r="P81">
-        <v>6.697509</v>
+        <v>6.553680000000001</v>
       </c>
       <c r="Q81">
-        <v>14.897509</v>
+        <v>14.75368</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1868446525254178</v>
+        <v>0.1933145907146572</v>
       </c>
       <c r="T81">
-        <v>2.052371551927045</v>
+        <v>2.146517035960396</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.589440202856926</v>
+        <v>1.569572200321215</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08906291814293144</v>
+        <v>0.08911845925552514</v>
       </c>
       <c r="C82">
-        <v>31.32315630661415</v>
+        <v>28.90232094218115</v>
       </c>
       <c r="D82">
-        <v>164.2631563066142</v>
+        <v>164.1253209421812</v>
       </c>
       <c r="E82">
-        <v>130.44</v>
+        <v>132.723</v>
       </c>
       <c r="F82">
-        <v>182.64</v>
+        <v>184.923</v>
       </c>
       <c r="G82">
         <v>49.7</v>
@@ -8011,28 +8011,28 @@
         <v>25.8</v>
       </c>
       <c r="M82">
-        <v>16.4376</v>
+        <v>16.64307</v>
       </c>
       <c r="N82">
-        <v>9.362400000000001</v>
+        <v>9.156929999999999</v>
       </c>
       <c r="O82">
-        <v>2.80872</v>
+        <v>2.747079</v>
       </c>
       <c r="P82">
-        <v>6.553680000000001</v>
+        <v>6.409851</v>
       </c>
       <c r="Q82">
-        <v>14.75368</v>
+        <v>14.609851</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1933145907146572</v>
+        <v>0.2004655750290797</v>
       </c>
       <c r="T82">
-        <v>2.146517035960396</v>
+        <v>2.250572570944626</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.569572200321215</v>
+        <v>1.550194765749348</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08911845925552514</v>
+        <v>0.08917400036811882</v>
       </c>
       <c r="C83">
-        <v>28.90232094218115</v>
+        <v>26.4817167027249</v>
       </c>
       <c r="D83">
-        <v>164.1253209421812</v>
+        <v>163.9877167027249</v>
       </c>
       <c r="E83">
-        <v>132.723</v>
+        <v>135.006</v>
       </c>
       <c r="F83">
-        <v>184.923</v>
+        <v>187.206</v>
       </c>
       <c r="G83">
         <v>49.7</v>
@@ -8093,28 +8093,28 @@
         <v>25.8</v>
       </c>
       <c r="M83">
-        <v>16.64307</v>
+        <v>16.84854</v>
       </c>
       <c r="N83">
-        <v>9.156929999999999</v>
+        <v>8.951460000000001</v>
       </c>
       <c r="O83">
-        <v>2.747079</v>
+        <v>2.685438</v>
       </c>
       <c r="P83">
-        <v>6.409851</v>
+        <v>6.266022000000001</v>
       </c>
       <c r="Q83">
-        <v>14.609851</v>
+        <v>14.466022</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2004655750290797</v>
+        <v>0.2084111131562157</v>
       </c>
       <c r="T83">
-        <v>2.250572570944626</v>
+        <v>2.366189832038215</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.550194765749348</v>
+        <v>1.531289951532893</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08917400036811882</v>
+        <v>0.08922954148071251</v>
       </c>
       <c r="C84">
-        <v>26.4817167027249</v>
+        <v>24.06134300740024</v>
       </c>
       <c r="D84">
-        <v>163.9877167027249</v>
+        <v>163.8503430074003</v>
       </c>
       <c r="E84">
-        <v>135.006</v>
+        <v>137.289</v>
       </c>
       <c r="F84">
-        <v>187.206</v>
+        <v>189.489</v>
       </c>
       <c r="G84">
         <v>49.7</v>
@@ -8175,28 +8175,28 @@
         <v>25.8</v>
       </c>
       <c r="M84">
-        <v>16.84854</v>
+        <v>17.05401</v>
       </c>
       <c r="N84">
-        <v>8.951460000000001</v>
+        <v>8.745989999999999</v>
       </c>
       <c r="O84">
-        <v>2.685438</v>
+        <v>2.623797</v>
       </c>
       <c r="P84">
-        <v>6.266022000000001</v>
+        <v>6.122192999999999</v>
       </c>
       <c r="Q84">
-        <v>14.466022</v>
+        <v>14.322193</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2084111131562157</v>
+        <v>0.2172914204747795</v>
       </c>
       <c r="T84">
-        <v>2.366189832038215</v>
+        <v>2.495409123848696</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.531289951532893</v>
+        <v>1.5128406750084</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08922954148071251</v>
+        <v>0.1265916614919882</v>
       </c>
       <c r="C85">
-        <v>24.06134300740024</v>
+        <v>-37.2761793030682</v>
       </c>
       <c r="D85">
-        <v>163.8503430074003</v>
+        <v>104.7958206969318</v>
       </c>
       <c r="E85">
-        <v>137.289</v>
+        <v>139.572</v>
       </c>
       <c r="F85">
-        <v>189.489</v>
+        <v>191.772</v>
       </c>
       <c r="G85">
         <v>49.7</v>
@@ -8257,45 +8257,45 @@
         <v>25.8</v>
       </c>
       <c r="M85">
-        <v>17.05401</v>
+        <v>28.15212960000001</v>
       </c>
       <c r="N85">
-        <v>8.745989999999999</v>
+        <v>-2.352129600000005</v>
       </c>
       <c r="O85">
-        <v>2.623797</v>
+        <v>-0.7056388800000014</v>
       </c>
       <c r="P85">
-        <v>6.122192999999999</v>
+        <v>-1.646490720000004</v>
       </c>
       <c r="Q85">
-        <v>14.322193</v>
+        <v>6.553509279999996</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2172914204747795</v>
+        <v>0.2323901313682905</v>
       </c>
       <c r="T85">
-        <v>2.495409123848696</v>
+        <v>2.71511376456897</v>
       </c>
       <c r="U85">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.3</v>
+        <v>0.2749347956965926</v>
       </c>
       <c r="W85">
-        <v>0.063</v>
+        <v>0.1064395719917402</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>1.5128406750084</v>
+        <v>0.9164493189886422</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1265916614919882</v>
+        <v>0.1276016614919882</v>
       </c>
       <c r="C86">
-        <v>-37.27617930306818</v>
+        <v>-40.57035995707423</v>
       </c>
       <c r="D86">
-        <v>104.7958206969318</v>
+        <v>103.7846400429258</v>
       </c>
       <c r="E86">
-        <v>139.572</v>
+        <v>141.855</v>
       </c>
       <c r="F86">
-        <v>191.772</v>
+        <v>194.055</v>
       </c>
       <c r="G86">
         <v>49.7</v>
@@ -8339,37 +8339,37 @@
         <v>25.8</v>
       </c>
       <c r="M86">
-        <v>28.1521296</v>
+        <v>28.487274</v>
       </c>
       <c r="N86">
-        <v>-2.352129600000001</v>
+        <v>-2.687274000000002</v>
       </c>
       <c r="O86">
-        <v>-0.7056388800000004</v>
+        <v>-0.8061822000000006</v>
       </c>
       <c r="P86">
-        <v>-1.646490720000001</v>
+        <v>-1.881091800000001</v>
       </c>
       <c r="Q86">
-        <v>6.553509279999998</v>
+        <v>6.318908199999997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2323901313682903</v>
+        <v>0.2448294734595098</v>
       </c>
       <c r="T86">
-        <v>2.715113764568968</v>
+        <v>2.896121348873567</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2749347956965927</v>
+        <v>0.2717002686883975</v>
       </c>
       <c r="W86">
-        <v>0.1064395719917402</v>
+        <v>0.1069144005565433</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9164493189886422</v>
+        <v>0.9056675622946583</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1276016614919882</v>
+        <v>0.1286116614919882</v>
       </c>
       <c r="C87">
-        <v>-40.57035995707423</v>
+        <v>-43.8452132262762</v>
       </c>
       <c r="D87">
-        <v>103.7846400429258</v>
+        <v>102.7927867737238</v>
       </c>
       <c r="E87">
-        <v>141.855</v>
+        <v>144.138</v>
       </c>
       <c r="F87">
-        <v>194.055</v>
+        <v>196.338</v>
       </c>
       <c r="G87">
         <v>49.7</v>
@@ -8421,37 +8421,37 @@
         <v>25.8</v>
       </c>
       <c r="M87">
-        <v>28.487274</v>
+        <v>28.8224184</v>
       </c>
       <c r="N87">
-        <v>-2.687274000000002</v>
+        <v>-3.022418399999999</v>
       </c>
       <c r="O87">
-        <v>-0.8061822000000006</v>
+        <v>-0.9067255199999997</v>
       </c>
       <c r="P87">
-        <v>-1.881091800000001</v>
+        <v>-2.11569288</v>
       </c>
       <c r="Q87">
-        <v>6.318908199999997</v>
+        <v>6.08430712</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2448294734595098</v>
+        <v>0.2590458644209033</v>
       </c>
       <c r="T87">
-        <v>2.896121348873567</v>
+        <v>3.102987159507393</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2717002686883975</v>
+        <v>0.2685409632385324</v>
       </c>
       <c r="W87">
-        <v>0.1069144005565433</v>
+        <v>0.1073781865965834</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9056675622946583</v>
+        <v>0.8951365441284413</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1286116614919882</v>
+        <v>0.1296216614919882</v>
       </c>
       <c r="C88">
-        <v>-43.8452132262762</v>
+        <v>-47.1012879913209</v>
       </c>
       <c r="D88">
-        <v>102.7927867737238</v>
+        <v>101.8197120086791</v>
       </c>
       <c r="E88">
-        <v>144.138</v>
+        <v>146.421</v>
       </c>
       <c r="F88">
-        <v>196.338</v>
+        <v>198.621</v>
       </c>
       <c r="G88">
         <v>49.7</v>
@@ -8503,37 +8503,37 @@
         <v>25.8</v>
       </c>
       <c r="M88">
-        <v>28.8224184</v>
+        <v>29.1575628</v>
       </c>
       <c r="N88">
-        <v>-3.022418399999999</v>
+        <v>-3.357562800000004</v>
       </c>
       <c r="O88">
-        <v>-0.9067255199999997</v>
+        <v>-1.007268840000001</v>
       </c>
       <c r="P88">
-        <v>-2.11569288</v>
+        <v>-2.350293960000003</v>
       </c>
       <c r="Q88">
-        <v>6.08430712</v>
+        <v>5.849706039999996</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2590458644209033</v>
+        <v>0.2754493924532804</v>
       </c>
       <c r="T88">
-        <v>3.102987159507393</v>
+        <v>3.3416784794695</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2685409632385324</v>
+        <v>0.2654542855001584</v>
       </c>
       <c r="W88">
-        <v>0.1073781865965834</v>
+        <v>0.1078313108885767</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8951365441284413</v>
+        <v>0.8848476183338615</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1296216614919882</v>
+        <v>0.1306316614919882</v>
       </c>
       <c r="C89">
-        <v>-47.1012879913209</v>
+        <v>-50.33911254412189</v>
       </c>
       <c r="D89">
-        <v>101.8197120086791</v>
+        <v>100.8648874558781</v>
       </c>
       <c r="E89">
-        <v>146.421</v>
+        <v>148.704</v>
       </c>
       <c r="F89">
-        <v>198.621</v>
+        <v>200.904</v>
       </c>
       <c r="G89">
         <v>49.7</v>
@@ -8585,37 +8585,37 @@
         <v>25.8</v>
       </c>
       <c r="M89">
-        <v>29.1575628</v>
+        <v>29.49270720000001</v>
       </c>
       <c r="N89">
-        <v>-3.357562800000004</v>
+        <v>-3.692707200000005</v>
       </c>
       <c r="O89">
-        <v>-1.007268840000001</v>
+        <v>-1.107812160000001</v>
       </c>
       <c r="P89">
-        <v>-2.350293960000003</v>
+        <v>-2.584895040000003</v>
       </c>
       <c r="Q89">
-        <v>5.849706039999996</v>
+        <v>5.615104959999996</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2754493924532804</v>
+        <v>0.2945868418243872</v>
       </c>
       <c r="T89">
-        <v>3.3416784794695</v>
+        <v>3.620151686091959</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2654542855001584</v>
+        <v>0.2624377595285657</v>
       </c>
       <c r="W89">
-        <v>0.1078313108885767</v>
+        <v>0.1082741369012066</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8848476183338615</v>
+        <v>0.8747925317618858</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1306316614919882</v>
+        <v>0.1316416614919882</v>
       </c>
       <c r="C90">
-        <v>-50.33911254412189</v>
+        <v>-53.55919554425549</v>
       </c>
       <c r="D90">
-        <v>100.8648874558781</v>
+        <v>99.92780445574451</v>
       </c>
       <c r="E90">
-        <v>148.704</v>
+        <v>150.987</v>
       </c>
       <c r="F90">
-        <v>200.904</v>
+        <v>203.187</v>
       </c>
       <c r="G90">
         <v>49.7</v>
@@ -8667,37 +8667,37 @@
         <v>25.8</v>
       </c>
       <c r="M90">
-        <v>29.49270720000001</v>
+        <v>29.82785160000001</v>
       </c>
       <c r="N90">
-        <v>-3.692707200000005</v>
+        <v>-4.027851600000005</v>
       </c>
       <c r="O90">
-        <v>-1.107812160000001</v>
+        <v>-1.208355480000002</v>
       </c>
       <c r="P90">
-        <v>-2.584895040000003</v>
+        <v>-2.819496120000004</v>
       </c>
       <c r="Q90">
-        <v>5.615104959999996</v>
+        <v>5.380503879999996</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2945868418243872</v>
+        <v>0.317203827444786</v>
       </c>
       <c r="T90">
-        <v>3.620151686091959</v>
+        <v>3.949256384827592</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2624377595285657</v>
+        <v>0.2594890206574582</v>
       </c>
       <c r="W90">
-        <v>0.1082741369012066</v>
+        <v>0.1087070117674851</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8747925317618858</v>
+        <v>0.8649634021915275</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1316416614919882</v>
+        <v>0.1326516614919882</v>
       </c>
       <c r="C91">
-        <v>-53.55919554425549</v>
+        <v>-56.76202692253543</v>
       </c>
       <c r="D91">
-        <v>99.92780445574451</v>
+        <v>99.00797307746461</v>
       </c>
       <c r="E91">
-        <v>150.987</v>
+        <v>153.27</v>
       </c>
       <c r="F91">
-        <v>203.187</v>
+        <v>205.47</v>
       </c>
       <c r="G91">
         <v>49.7</v>
@@ -8749,37 +8749,37 @@
         <v>25.8</v>
       </c>
       <c r="M91">
-        <v>29.82785160000001</v>
+        <v>30.16299600000001</v>
       </c>
       <c r="N91">
-        <v>-4.027851600000005</v>
+        <v>-4.362996000000006</v>
       </c>
       <c r="O91">
-        <v>-1.208355480000002</v>
+        <v>-1.308898800000002</v>
       </c>
       <c r="P91">
-        <v>-2.819496120000004</v>
+        <v>-3.054097200000005</v>
       </c>
       <c r="Q91">
-        <v>5.380503879999996</v>
+        <v>5.145902799999995</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.317203827444786</v>
+        <v>0.3443442101892646</v>
       </c>
       <c r="T91">
-        <v>3.949256384827592</v>
+        <v>4.344182023310351</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2594890206574582</v>
+        <v>0.2566058093168198</v>
       </c>
       <c r="W91">
-        <v>0.1087070117674851</v>
+        <v>0.1091302671922909</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8649634021915275</v>
+        <v>0.8553526977227327</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1326516614919882</v>
+        <v>0.1336616614919882</v>
       </c>
       <c r="C92">
-        <v>-56.76202692253543</v>
+        <v>-59.94807873513733</v>
       </c>
       <c r="D92">
-        <v>99.00797307746461</v>
+        <v>98.10492126486267</v>
       </c>
       <c r="E92">
-        <v>153.27</v>
+        <v>155.553</v>
       </c>
       <c r="F92">
-        <v>205.47</v>
+        <v>207.753</v>
       </c>
       <c r="G92">
         <v>49.7</v>
@@ -8831,37 +8831,37 @@
         <v>25.8</v>
       </c>
       <c r="M92">
-        <v>30.16299600000001</v>
+        <v>30.4981404</v>
       </c>
       <c r="N92">
-        <v>-4.362996000000006</v>
+        <v>-4.698140400000003</v>
       </c>
       <c r="O92">
-        <v>-1.308898800000002</v>
+        <v>-1.409442120000001</v>
       </c>
       <c r="P92">
-        <v>-3.054097200000005</v>
+        <v>-3.288698280000002</v>
       </c>
       <c r="Q92">
-        <v>5.145902799999995</v>
+        <v>4.911301719999997</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3443442101892646</v>
+        <v>0.377515789099183</v>
       </c>
       <c r="T92">
-        <v>4.344182023310351</v>
+        <v>4.82686891478928</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2566058093168198</v>
+        <v>0.2537859652583933</v>
       </c>
       <c r="W92">
-        <v>0.1091302671922909</v>
+        <v>0.1095442203000679</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8553526977227327</v>
+        <v>0.8459532175279775</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1336616614919882</v>
+        <v>0.1346716614919883</v>
       </c>
       <c r="C93">
-        <v>-59.94807873513733</v>
+        <v>-63.11780597140475</v>
       </c>
       <c r="D93">
-        <v>98.10492126486267</v>
+        <v>97.21819402859528</v>
       </c>
       <c r="E93">
-        <v>155.553</v>
+        <v>157.836</v>
       </c>
       <c r="F93">
-        <v>207.753</v>
+        <v>210.036</v>
       </c>
       <c r="G93">
         <v>49.7</v>
@@ -8913,37 +8913,37 @@
         <v>25.8</v>
       </c>
       <c r="M93">
-        <v>30.4981404</v>
+        <v>30.83328480000001</v>
       </c>
       <c r="N93">
-        <v>-4.698140400000003</v>
+        <v>-5.033284800000008</v>
       </c>
       <c r="O93">
-        <v>-1.409442120000001</v>
+        <v>-1.509985440000002</v>
       </c>
       <c r="P93">
-        <v>-3.288698280000002</v>
+        <v>-3.523299360000006</v>
       </c>
       <c r="Q93">
-        <v>4.911301719999997</v>
+        <v>4.676700639999994</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.377515789099183</v>
+        <v>0.418980262736581</v>
       </c>
       <c r="T93">
-        <v>4.82686891478928</v>
+        <v>5.430227529137942</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2537859652583933</v>
+        <v>0.2510274221577585</v>
       </c>
       <c r="W93">
-        <v>0.1095442203000679</v>
+        <v>0.1099491744272411</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8459532175279775</v>
+        <v>0.836758073859195</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1346716614919883</v>
+        <v>0.1356816614919882</v>
       </c>
       <c r="C94">
-        <v>-63.11780597140475</v>
+        <v>-66.27164731823709</v>
       </c>
       <c r="D94">
-        <v>97.21819402859528</v>
+        <v>96.34735268176293</v>
       </c>
       <c r="E94">
-        <v>157.836</v>
+        <v>160.119</v>
       </c>
       <c r="F94">
-        <v>210.036</v>
+        <v>212.319</v>
       </c>
       <c r="G94">
         <v>49.7</v>
@@ -8995,37 +8995,37 @@
         <v>25.8</v>
       </c>
       <c r="M94">
-        <v>30.83328480000001</v>
+        <v>31.16842920000001</v>
       </c>
       <c r="N94">
-        <v>-5.033284800000008</v>
+        <v>-5.368429200000005</v>
       </c>
       <c r="O94">
-        <v>-1.509985440000002</v>
+        <v>-1.610528760000001</v>
       </c>
       <c r="P94">
-        <v>-3.523299360000006</v>
+        <v>-3.757900440000004</v>
       </c>
       <c r="Q94">
-        <v>4.676700639999994</v>
+        <v>4.442099559999996</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.418980262736581</v>
+        <v>0.4722917288418069</v>
       </c>
       <c r="T94">
-        <v>5.430227529137942</v>
+        <v>6.205974319014791</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2510274221577585</v>
+        <v>0.2483282025646643</v>
       </c>
       <c r="W94">
-        <v>0.1099491744272411</v>
+        <v>0.1103454198635073</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.836758073859195</v>
+        <v>0.8277606752155477</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1356816614919882</v>
+        <v>0.1366916614919882</v>
       </c>
       <c r="C95">
-        <v>-66.27164731823709</v>
+        <v>-69.41002588376165</v>
       </c>
       <c r="D95">
-        <v>96.34735268176293</v>
+        <v>95.4919741162384</v>
       </c>
       <c r="E95">
-        <v>160.119</v>
+        <v>162.402</v>
       </c>
       <c r="F95">
-        <v>212.319</v>
+        <v>214.602</v>
       </c>
       <c r="G95">
         <v>49.7</v>
@@ -9077,37 +9077,37 @@
         <v>25.8</v>
       </c>
       <c r="M95">
-        <v>31.16842920000001</v>
+        <v>31.50357360000001</v>
       </c>
       <c r="N95">
-        <v>-5.368429200000005</v>
+        <v>-5.703573600000006</v>
       </c>
       <c r="O95">
-        <v>-1.610528760000001</v>
+        <v>-1.711072080000002</v>
       </c>
       <c r="P95">
-        <v>-3.757900440000004</v>
+        <v>-3.992501520000004</v>
       </c>
       <c r="Q95">
-        <v>4.442099559999996</v>
+        <v>4.207498479999995</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4722917288418069</v>
+        <v>0.5433736836487748</v>
       </c>
       <c r="T95">
-        <v>6.205974319014791</v>
+        <v>7.240303372183924</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2483282025646643</v>
+        <v>0.2456864131756785</v>
       </c>
       <c r="W95">
-        <v>0.1103454198635073</v>
+        <v>0.1107332345458104</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8277606752155477</v>
+        <v>0.8189547105855951</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1366916614919882</v>
+        <v>0.1377016614919882</v>
       </c>
       <c r="C96">
-        <v>-69.41002588376165</v>
+        <v>-72.53334988279468</v>
       </c>
       <c r="D96">
-        <v>95.4919741162384</v>
+        <v>94.65165011720535</v>
       </c>
       <c r="E96">
-        <v>162.402</v>
+        <v>164.685</v>
       </c>
       <c r="F96">
-        <v>214.602</v>
+        <v>216.885</v>
       </c>
       <c r="G96">
         <v>49.7</v>
@@ -9159,37 +9159,37 @@
         <v>25.8</v>
       </c>
       <c r="M96">
-        <v>31.50357360000001</v>
+        <v>31.83871800000001</v>
       </c>
       <c r="N96">
-        <v>-5.703573600000006</v>
+        <v>-6.038718000000006</v>
       </c>
       <c r="O96">
-        <v>-1.711072080000002</v>
+        <v>-1.811615400000002</v>
       </c>
       <c r="P96">
-        <v>-3.992501520000004</v>
+        <v>-4.227102600000005</v>
       </c>
       <c r="Q96">
-        <v>4.207498479999995</v>
+        <v>3.972897399999995</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5433736836487748</v>
+        <v>0.64288842037853</v>
       </c>
       <c r="T96">
-        <v>7.240303372183924</v>
+        <v>8.688364046620713</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2456864131756785</v>
+        <v>0.2431002404054082</v>
       </c>
       <c r="W96">
-        <v>0.1107332345458104</v>
+        <v>0.1111128847084861</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8189547105855951</v>
+        <v>0.8103341346846942</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1377016614919882</v>
+        <v>0.1387116614919883</v>
       </c>
       <c r="C97">
-        <v>-72.53334988279468</v>
+        <v>-75.6420132864269</v>
       </c>
       <c r="D97">
-        <v>94.65165011720535</v>
+        <v>93.82598671357313</v>
       </c>
       <c r="E97">
-        <v>164.685</v>
+        <v>166.968</v>
       </c>
       <c r="F97">
-        <v>216.885</v>
+        <v>219.168</v>
       </c>
       <c r="G97">
         <v>49.7</v>
@@ -9241,37 +9241,37 @@
         <v>25.8</v>
       </c>
       <c r="M97">
-        <v>31.83871800000001</v>
+        <v>32.17386240000001</v>
       </c>
       <c r="N97">
-        <v>-6.038718000000006</v>
+        <v>-6.373862400000011</v>
       </c>
       <c r="O97">
-        <v>-1.811615400000002</v>
+        <v>-1.912158720000003</v>
       </c>
       <c r="P97">
-        <v>-4.227102600000005</v>
+        <v>-4.461703680000007</v>
       </c>
       <c r="Q97">
-        <v>3.972897399999995</v>
+        <v>3.738296319999992</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.64288842037853</v>
+        <v>0.7921605254731628</v>
       </c>
       <c r="T97">
-        <v>8.688364046620713</v>
+        <v>10.8604550582759</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2431002404054082</v>
+        <v>0.2405679462345185</v>
       </c>
       <c r="W97">
-        <v>0.1111128847084861</v>
+        <v>0.1114846254927727</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8103341346846942</v>
+        <v>0.8018931541150618</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1387116614919882</v>
+        <v>0.1945126238340775</v>
       </c>
       <c r="C98">
-        <v>-75.64201328642682</v>
+        <v>-108.4381580388678</v>
       </c>
       <c r="D98">
-        <v>93.82598671357319</v>
+        <v>63.31284196113215</v>
       </c>
       <c r="E98">
-        <v>166.968</v>
+        <v>169.251</v>
       </c>
       <c r="F98">
-        <v>219.168</v>
+        <v>221.451</v>
       </c>
       <c r="G98">
         <v>49.7</v>
@@ -9323,45 +9323,45 @@
         <v>25.8</v>
       </c>
       <c r="M98">
-        <v>32.1738624</v>
+        <v>44.4673608</v>
       </c>
       <c r="N98">
-        <v>-6.373862400000004</v>
+        <v>-18.6673608</v>
       </c>
       <c r="O98">
-        <v>-1.912158720000001</v>
+        <v>-5.60020824</v>
       </c>
       <c r="P98">
-        <v>-4.461703680000003</v>
+        <v>-13.06715256</v>
       </c>
       <c r="Q98">
-        <v>3.738296319999996</v>
+        <v>-4.867152560000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7921605254731607</v>
+        <v>1.121312778700523</v>
       </c>
       <c r="T98">
-        <v>10.86045505827587</v>
+        <v>15.65002140255669</v>
       </c>
       <c r="U98">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.2405679462345186</v>
+        <v>0.174060251401293</v>
       </c>
       <c r="W98">
-        <v>0.1114846254927727</v>
+        <v>0.1658487015186204</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.801893154115062</v>
+        <v>0.5802008380043099</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1945126238340775</v>
+        <v>0.1960626238340775</v>
       </c>
       <c r="C99">
-        <v>-108.4381580388678</v>
+        <v>-111.287971403072</v>
       </c>
       <c r="D99">
-        <v>63.31284196113215</v>
+        <v>62.746028596928</v>
       </c>
       <c r="E99">
-        <v>169.251</v>
+        <v>171.534</v>
       </c>
       <c r="F99">
-        <v>221.451</v>
+        <v>223.734</v>
       </c>
       <c r="G99">
         <v>49.7</v>
@@ -9405,37 +9405,37 @@
         <v>25.8</v>
       </c>
       <c r="M99">
-        <v>44.4673608</v>
+        <v>44.9257872</v>
       </c>
       <c r="N99">
-        <v>-18.6673608</v>
+        <v>-19.1257872</v>
       </c>
       <c r="O99">
-        <v>-5.60020824</v>
+        <v>-5.73773616</v>
       </c>
       <c r="P99">
-        <v>-13.06715256</v>
+        <v>-13.38805104</v>
       </c>
       <c r="Q99">
-        <v>-4.867152560000001</v>
+        <v>-5.188051040000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.121312778700523</v>
+        <v>1.659069168050784</v>
       </c>
       <c r="T99">
-        <v>15.65002140255669</v>
+        <v>23.47503210383503</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.174060251401293</v>
+        <v>0.172284126386994</v>
       </c>
       <c r="W99">
-        <v>0.1658487015186204</v>
+        <v>0.1662053474214916</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5802008380043099</v>
+        <v>0.5742804212899801</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1960626238340775</v>
+        <v>0.1976126238340775</v>
       </c>
       <c r="C100">
-        <v>-111.287971403072</v>
+        <v>-114.1277259343597</v>
       </c>
       <c r="D100">
-        <v>62.746028596928</v>
+        <v>62.18927406564033</v>
       </c>
       <c r="E100">
-        <v>171.534</v>
+        <v>173.817</v>
       </c>
       <c r="F100">
-        <v>223.734</v>
+        <v>226.017</v>
       </c>
       <c r="G100">
         <v>49.7</v>
@@ -9487,37 +9487,37 @@
         <v>25.8</v>
       </c>
       <c r="M100">
-        <v>44.9257872</v>
+        <v>45.3842136</v>
       </c>
       <c r="N100">
-        <v>-19.1257872</v>
+        <v>-19.5842136</v>
       </c>
       <c r="O100">
-        <v>-5.73773616</v>
+        <v>-5.87526408</v>
       </c>
       <c r="P100">
-        <v>-13.38805104</v>
+        <v>-13.70894952</v>
       </c>
       <c r="Q100">
-        <v>-5.188051040000001</v>
+        <v>-5.508949520000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.659069168050784</v>
+        <v>3.272338336101567</v>
       </c>
       <c r="T100">
-        <v>23.47503210383503</v>
+        <v>46.95006420767006</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.172284126386994</v>
+        <v>0.1705438826861153</v>
       </c>
       <c r="W100">
-        <v>0.1662053474214916</v>
+        <v>0.166554788356628</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5742804212899801</v>
+        <v>0.5684796089537177</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1976126238340775</v>
-      </c>
-      <c r="C101">
-        <v>-114.1277259343597</v>
-      </c>
-      <c r="D101">
-        <v>62.18927406564033</v>
-      </c>
-      <c r="E101">
-        <v>173.817</v>
-      </c>
-      <c r="F101">
-        <v>226.017</v>
-      </c>
-      <c r="G101">
-        <v>49.7</v>
-      </c>
-      <c r="H101">
-        <v>176.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>34</v>
-      </c>
-      <c r="K101">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L101">
-        <v>25.8</v>
-      </c>
-      <c r="M101">
-        <v>45.3842136</v>
-      </c>
-      <c r="N101">
-        <v>-19.5842136</v>
-      </c>
-      <c r="O101">
-        <v>-5.87526408</v>
-      </c>
-      <c r="P101">
-        <v>-13.70894952</v>
-      </c>
-      <c r="Q101">
-        <v>-5.508949520000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.272338336101567</v>
-      </c>
-      <c r="T101">
-        <v>46.95006420767006</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1705438826861153</v>
-      </c>
-      <c r="W101">
-        <v>0.166554788356628</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5684796089537177</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
